--- a/MVP/INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/batch01_vocabulary_and_fixture_tracker.xlsx
+++ b/MVP/INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/batch01_vocabulary_and_fixture_tracker.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0faf2a56144e4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REQUIREMENTS" sheetId="2" r:id="R9d4c696621244487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PREFLIGHT" sheetId="3" r:id="Rd51b033963dc4213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRAFT_TERMS" sheetId="4" r:id="R38f1bdc939b24998"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R2_INDEX_GAPS" sheetId="5" r:id="R6331fea50eab468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEVELOPMENT_TERMS" sheetId="6" r:id="Rac9404d1a68749ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OWNERSHIP" sheetId="7" r:id="R95a26f3a567247ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STABILIZATION" sheetId="8" r:id="R1422bbf4a21b48de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RDF_CASES" sheetId="9" r:id="Rec22d086943a4ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALIBRATION_ANALYSIS" sheetId="10" r:id="R7499bc01829a493b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="11" r:id="R9966a00f4d4345f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra8d8d99e80d74663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REQUIREMENTS" sheetId="2" r:id="R3fca6bb54de945ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PREFLIGHT" sheetId="3" r:id="Rdd62c9ecce1a4fdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRAFT_TERMS" sheetId="4" r:id="R154de334951b43e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R2_INDEX_GAPS" sheetId="5" r:id="R3d3e9a3782f64eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEVELOPMENT_TERMS" sheetId="6" r:id="R32f0284688b8405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OWNERSHIP" sheetId="7" r:id="R266432a4687d4d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STABILIZATION" sheetId="8" r:id="R83b7eda837f04527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RDF_CASES" sheetId="9" r:id="R01f295e3ecbd4db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALIBRATION_ANALYSIS" sheetId="10" r:id="R3d1b34203a864503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="11" r:id="R9336a636944e45e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_OWNERSHIP" displayName="T_OWNERSHIP" ref="A4:F539" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_OWNERSHIP" displayName="T_OWNERSHIP" ref="A4:F538" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="REQUIREMENT_ID"/>
     <x:tableColumn id="2" name="TARGET_OWNER"/>
@@ -793,7 +793,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_STABILIZATION" displayName="T_STABILIZATION" ref="A4:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_STABILIZATION" displayName="T_STABILIZATION" ref="A4:E14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="REQUIREMENT_ID"/>
     <x:tableColumn id="2" name="FAILURE_CLASS"/>
@@ -1102,7 +1102,7 @@
         <x:v>DEVELOPMENT BINDING</x:v>
       </x:c>
       <x:c r="B11" s="38" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8-STABILIZATION</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
@@ -1140,7 +1140,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf2c6a2c5b847b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2ffd65ccc847c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1627,7 +1627,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0696af61c23456d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R408c5f914f844a57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1813,7 +1813,7 @@
         <x:v>VOCABULARY</x:v>
       </x:c>
       <x:c r="B18" s="19" t="str">
-        <x:v>R2 is the source baseline; R8 stabilization preserves R7 and repairs two existing-term context gaps without adding vocabulary terms.</x:v>
+        <x:v>R2 is the source baseline; R8.1 preserves the R8 confirmation evidence and records three post-confirmation schema/index corrections without adding vocabulary terms.</x:v>
       </x:c>
       <x:c r="C18" s="19" t="str"/>
       <x:c r="D18" s="19" t="str"/>
@@ -1833,7 +1833,7 @@
         <x:v>NEXT GATE</x:v>
       </x:c>
       <x:c r="B20" s="19" t="str">
-        <x:v>Run a small non-official confirmation set only if desired, then scale to the remaining eligible requirements. Do not reopen first-50 prompt tuning unless a new general failure class is proven.</x:v>
+        <x:v>R8 confirmation found no remaining vocabulary-name gap. R8.1 now needs only a no-API fixture/schema recheck, after which generation may scale with RDF evaluation kept separate.</x:v>
       </x:c>
       <x:c r="C20" s="19" t="str"/>
       <x:c r="D20" s="19" t="str"/>
@@ -2850,10 +2850,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M23" s="54" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N23" s="38" t="str">
-        <x:v>bowRakeAtQuarterBreadth | clampedHullGeometryTerm | coefficientC3 | coefficientC4 | coefficientC5 | coefficientF1 | coefficientF2 | coefficientF3 | coefficientF4 | coefficientG1 | coefficientG2 | coefficientG3 | constructionStageDate | flareAngle | iceClassDraught | kilogramPerSquareMetreSquareSecondUnit | kilogramPerSquareSecondUnit | newtonPerMetreToPowerOnePointFiveUnit | shipBreadth | shipLength | waterlineAngleAtQuarterBreadth</x:v>
+        <x:v>bowRakeAtQuarterBreadth | clampedHullGeometryTerm | coefficientC3 | coefficientC4 | coefficientC5 | coefficientF1 | coefficientF2 | coefficientF3 | coefficientF4 | coefficientG1 | coefficientG2 | coefficientG3 | flareAngle | iceClassDraught | kilogramPerSquareMetreSquareSecondUnit | kilogramPerSquareSecondUnit | newtonPerMetreToPowerOnePointFiveUnit | shipBreadth | shipLength | waterlineAngleAtQuarterBreadth</x:v>
       </x:c>
       <x:c r="O23" s="38" t="str">
         <x:v>Set C_3 = 845 kg/(m^2*s^2), C_4 = 42 kg/(m^2*s^2), C_5 = 825 kg/s^2 and psi = atan(tan(phi_2)/sin(alpha)). Clamp ((L*T)/B^2)^3 to the inclusive interval [5, 20].</x:v>
@@ -4319,7 +4319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e3dd80835a04560"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf84ac9af75a44a01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6126,7 +6126,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5ed2f42da544584"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R574a0c90041545ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8472,7 +8472,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09b8e62c42bf41ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R202b7773798d408a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9863,7 +9863,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c7d45a6b81d4915"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08df3efcb2c84d46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13574,7 +13574,9 @@
         <x:v>http://qudt.org/schema/qudt/QuantityValue</x:v>
       </x:c>
       <x:c r="E126" s="35" t="str"/>
-      <x:c r="F126" s="35" t="str"/>
+      <x:c r="F126" s="35" t="str">
+        <x:v>N</x:v>
+      </x:c>
       <x:c r="G126" s="38" t="str">
         <x:v>TRF-025 | TRF-026</x:v>
       </x:c>
@@ -13602,7 +13604,9 @@
         <x:v>http://qudt.org/schema/qudt/QuantityValue</x:v>
       </x:c>
       <x:c r="E127" s="35" t="str"/>
-      <x:c r="F127" s="35" t="str"/>
+      <x:c r="F127" s="35" t="str">
+        <x:v>N</x:v>
+      </x:c>
       <x:c r="G127" s="38" t="str">
         <x:v>TRF-025 | TRF-026</x:v>
       </x:c>
@@ -41647,7 +41651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44c6a23fed4d49d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123dd78203b14531"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44612,7 +44616,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>constructionStageDate</x:v>
+        <x:v>flareAngle</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>ship</x:v>
@@ -44632,7 +44636,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>flareAngle</x:v>
+        <x:v>iceClassDraught</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>ship</x:v>
@@ -44652,7 +44656,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>iceClassDraught</x:v>
+        <x:v>kilogramPerSquareMetreSquareSecondUnit</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>ship</x:v>
@@ -44672,7 +44676,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>kilogramPerSquareMetreSquareSecondUnit</x:v>
+        <x:v>kilogramPerSquareSecondUnit</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>ship</x:v>
@@ -44692,7 +44696,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>kilogramPerSquareSecondUnit</x:v>
+        <x:v>newtonPerMetreToPowerOnePointFiveUnit</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>ship</x:v>
@@ -44712,7 +44716,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>newtonPerMetreToPowerOnePointFiveUnit</x:v>
+        <x:v>shipBreadth</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>ship</x:v>
@@ -44732,7 +44736,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>shipBreadth</x:v>
+        <x:v>shipLength</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>ship</x:v>
@@ -44752,7 +44756,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>shipLength</x:v>
+        <x:v>waterlineAngleAtQuarterBreadth</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>ship</x:v>
@@ -44766,20 +44770,18 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="38" t="str">
-        <x:v>TRF-022</x:v>
+        <x:v>TRF-023</x:v>
       </x:c>
       <x:c r="B166" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>waterlineAngleAtQuarterBreadth</x:v>
+        <x:v>applicableIceClassRegulationEdition</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
-      <x:c r="E166" s="35" t="str">
-        <x:v>Use the supported XPath math-function IRIs math:sin, math:tan, and math:atan from http://www.w3.org/2005/xpath-functions/math# for psi = atan(tan(phi2)/sin(alpha)); include degree/radian conversion, singular-input rejection, and tolerance comparison. | Apply Table 3-2 constants and clamp ((L*T)/B^2)^3 to the inclusive interval [5,20].</x:v>
-      </x:c>
+      <x:c r="E166" s="35" t="str"/>
       <x:c r="F166" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -44792,7 +44794,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>applicableIceClassRegulationEdition</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>ship</x:v>
@@ -44810,7 +44812,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>iceClassRuleEdition1985</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>ship</x:v>
@@ -44828,7 +44830,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>iceClassRuleEdition1985</x:v>
+        <x:v>maximumContinuousRatingPower</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>ship</x:v>
@@ -44846,7 +44848,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>maximumContinuousRatingPower</x:v>
+        <x:v>requiredPowerUnder1985Rules</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>ship</x:v>
@@ -44858,13 +44860,13 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="38" t="str">
-        <x:v>TRF-023</x:v>
+        <x:v>TRF-024</x:v>
       </x:c>
       <x:c r="B171" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>requiredPowerUnder1985Rules</x:v>
+        <x:v>assessmentDate</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>ship</x:v>
@@ -44882,7 +44884,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>assessmentDate</x:v>
+        <x:v>constructionStageDate</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>ship</x:v>
@@ -44900,7 +44902,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>constructionStageDate</x:v>
+        <x:v>deliveryDate</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>ship</x:v>
@@ -44918,7 +44920,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>deliveryDate</x:v>
+        <x:v>engineOutputComplianceMethod</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>ship</x:v>
@@ -44936,7 +44938,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>engineOutputComplianceMethod</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>ship</x:v>
@@ -44954,7 +44956,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>traficom2017Section3Point2Point2Method</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>ship</x:v>
@@ -44972,7 +44974,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>traficom2017Section3Point2Point2Method</x:v>
+        <x:v>traficom2017Section3Point2Point4Method</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>ship</x:v>
@@ -44984,18 +44986,20 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="38" t="str">
-        <x:v>TRF-024</x:v>
+        <x:v>TRF-025</x:v>
       </x:c>
       <x:c r="B178" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>traficom2017Section3Point2Point4Method</x:v>
+        <x:v>brashIceResistanceCoefficientC1</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
-      <x:c r="E178" s="35" t="str"/>
+      <x:c r="E178" s="35" t="str">
+        <x:v>Apply only to IA Super ships with bulbousBowPresent=false; require exactly one controlled iceClass and one boolean bulbousBowPresent before branch selection. | Validate C1 and C2 in their original value domains with numerical tolerance and reject non-positive L, B, or T operands.</x:v>
+      </x:c>
       <x:c r="F178" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -45008,7 +45012,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>brashIceResistanceCoefficientC1</x:v>
+        <x:v>brashIceResistanceCoefficientC2</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>ship</x:v>
@@ -45028,7 +45032,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>brashIceResistanceCoefficientC2</x:v>
+        <x:v>bulbousBowPresent</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>ship</x:v>
@@ -45048,7 +45052,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>bulbousBowPresent</x:v>
+        <x:v>coefficientF1</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>ship</x:v>
@@ -45068,7 +45072,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>coefficientF1</x:v>
+        <x:v>coefficientF2</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>ship</x:v>
@@ -45088,7 +45092,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>coefficientF2</x:v>
+        <x:v>coefficientF3</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>ship</x:v>
@@ -45108,7 +45112,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>coefficientF3</x:v>
+        <x:v>coefficientF4</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>ship</x:v>
@@ -45128,7 +45132,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>coefficientF4</x:v>
+        <x:v>coefficientG1</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>ship</x:v>
@@ -45148,7 +45152,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>coefficientG1</x:v>
+        <x:v>coefficientG2</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>ship</x:v>
@@ -45168,7 +45172,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>coefficientG2</x:v>
+        <x:v>coefficientG3</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>ship</x:v>
@@ -45188,7 +45192,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>coefficientG3</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>ship</x:v>
@@ -45208,7 +45212,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>iceClassDraught</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>ship</x:v>
@@ -45228,7 +45232,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>iceClassDraught</x:v>
+        <x:v>newtonPerMetreToPowerOnePointFiveUnit</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>ship</x:v>
@@ -45248,7 +45252,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>newtonPerMetreToPowerOnePointFiveUnit</x:v>
+        <x:v>shipBreadth</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>ship</x:v>
@@ -45268,7 +45272,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>shipBreadth</x:v>
+        <x:v>shipLength</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>ship</x:v>
@@ -45282,19 +45286,19 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="38" t="str">
-        <x:v>TRF-025</x:v>
+        <x:v>TRF-026</x:v>
       </x:c>
       <x:c r="B193" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>shipLength</x:v>
+        <x:v>brashIceResistanceCoefficientC1</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="E193" s="35" t="str">
-        <x:v>Apply only to IA Super ships with bulbousBowPresent=false; require exactly one controlled iceClass and one boolean bulbousBowPresent before branch selection. | Validate C1 and C2 in their original value domains with numerical tolerance and reject non-positive L, B, or T operands.</x:v>
+        <x:v>Require exactly one controlled iceClass first. Non-IA-Super ships are non-applicable without bulb data; IA Super requires exactly one bulbousBowPresent value, false is non-applicable, and true activates the C1/C2 formula checks.</x:v>
       </x:c>
       <x:c r="F193" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
@@ -45308,7 +45312,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>brashIceResistanceCoefficientC1</x:v>
+        <x:v>brashIceResistanceCoefficientC2</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>ship</x:v>
@@ -45328,7 +45332,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>brashIceResistanceCoefficientC2</x:v>
+        <x:v>bulbousBowPresent</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>ship</x:v>
@@ -45348,7 +45352,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>bulbousBowPresent</x:v>
+        <x:v>coefficientF1</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>ship</x:v>
@@ -45368,7 +45372,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>coefficientF1</x:v>
+        <x:v>coefficientF2</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>ship</x:v>
@@ -45388,7 +45392,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>coefficientF2</x:v>
+        <x:v>coefficientF3</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>ship</x:v>
@@ -45408,7 +45412,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>coefficientF3</x:v>
+        <x:v>coefficientF4</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>ship</x:v>
@@ -45428,7 +45432,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>coefficientF4</x:v>
+        <x:v>coefficientG1</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
         <x:v>ship</x:v>
@@ -45448,7 +45452,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>coefficientG1</x:v>
+        <x:v>coefficientG2</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
         <x:v>ship</x:v>
@@ -45468,7 +45472,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>coefficientG2</x:v>
+        <x:v>coefficientG3</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
         <x:v>ship</x:v>
@@ -45488,7 +45492,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C203" s="35" t="str">
-        <x:v>coefficientG3</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D203" s="35" t="str">
         <x:v>ship</x:v>
@@ -45508,7 +45512,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C204" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>iceClassDraught</x:v>
       </x:c>
       <x:c r="D204" s="35" t="str">
         <x:v>ship</x:v>
@@ -45528,7 +45532,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C205" s="35" t="str">
-        <x:v>iceClassDraught</x:v>
+        <x:v>shipBreadth</x:v>
       </x:c>
       <x:c r="D205" s="35" t="str">
         <x:v>ship</x:v>
@@ -45548,7 +45552,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C206" s="35" t="str">
-        <x:v>shipBreadth</x:v>
+        <x:v>shipLength</x:v>
       </x:c>
       <x:c r="D206" s="35" t="str">
         <x:v>ship</x:v>
@@ -45562,19 +45566,19 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="38" t="str">
-        <x:v>TRF-026</x:v>
+        <x:v>TRF-027</x:v>
       </x:c>
       <x:c r="B207" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C207" s="35" t="str">
-        <x:v>shipLength</x:v>
+        <x:v>clampedHullGeometryTerm</x:v>
       </x:c>
       <x:c r="D207" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="E207" s="35" t="str">
-        <x:v>Require exactly one controlled iceClass first. Non-IA-Super ships are non-applicable without bulb data; IA Super requires exactly one bulbousBowPresent value, false is non-applicable, and true activates the C1/C2 formula checks.</x:v>
+        <x:v>Require exactly one controlled iceClass before applicability branching; apply the Table 3-3 and clamped-geometry rules only to IA Super or IA ships with constructionStageDate before 1 September 2003.</x:v>
       </x:c>
       <x:c r="F207" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
@@ -45588,7 +45592,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C208" s="35" t="str">
-        <x:v>clampedHullGeometryTerm</x:v>
+        <x:v>coefficientC3</x:v>
       </x:c>
       <x:c r="D208" s="35" t="str">
         <x:v>ship</x:v>
@@ -45608,7 +45612,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C209" s="35" t="str">
-        <x:v>coefficientC3</x:v>
+        <x:v>coefficientC4</x:v>
       </x:c>
       <x:c r="D209" s="35" t="str">
         <x:v>ship</x:v>
@@ -45628,7 +45632,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C210" s="35" t="str">
-        <x:v>coefficientC4</x:v>
+        <x:v>coefficientC5</x:v>
       </x:c>
       <x:c r="D210" s="35" t="str">
         <x:v>ship</x:v>
@@ -45648,7 +45652,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C211" s="35" t="str">
-        <x:v>coefficientC5</x:v>
+        <x:v>coefficientF1</x:v>
       </x:c>
       <x:c r="D211" s="35" t="str">
         <x:v>ship</x:v>
@@ -45668,7 +45672,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C212" s="35" t="str">
-        <x:v>coefficientF1</x:v>
+        <x:v>coefficientF2</x:v>
       </x:c>
       <x:c r="D212" s="35" t="str">
         <x:v>ship</x:v>
@@ -45688,7 +45692,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C213" s="35" t="str">
-        <x:v>coefficientF2</x:v>
+        <x:v>coefficientF3</x:v>
       </x:c>
       <x:c r="D213" s="35" t="str">
         <x:v>ship</x:v>
@@ -45708,7 +45712,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C214" s="35" t="str">
-        <x:v>coefficientF3</x:v>
+        <x:v>coefficientF4</x:v>
       </x:c>
       <x:c r="D214" s="35" t="str">
         <x:v>ship</x:v>
@@ -45728,7 +45732,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C215" s="35" t="str">
-        <x:v>coefficientF4</x:v>
+        <x:v>coefficientG1</x:v>
       </x:c>
       <x:c r="D215" s="35" t="str">
         <x:v>ship</x:v>
@@ -45748,7 +45752,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C216" s="35" t="str">
-        <x:v>coefficientG1</x:v>
+        <x:v>coefficientG2</x:v>
       </x:c>
       <x:c r="D216" s="35" t="str">
         <x:v>ship</x:v>
@@ -45768,7 +45772,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C217" s="35" t="str">
-        <x:v>coefficientG2</x:v>
+        <x:v>coefficientG3</x:v>
       </x:c>
       <x:c r="D217" s="35" t="str">
         <x:v>ship</x:v>
@@ -45788,7 +45792,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C218" s="35" t="str">
-        <x:v>coefficientG3</x:v>
+        <x:v>constructionStageDate</x:v>
       </x:c>
       <x:c r="D218" s="35" t="str">
         <x:v>ship</x:v>
@@ -45808,7 +45812,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C219" s="35" t="str">
-        <x:v>constructionStageDate</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D219" s="35" t="str">
         <x:v>ship</x:v>
@@ -45828,7 +45832,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C220" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>iceClassDraught</x:v>
       </x:c>
       <x:c r="D220" s="35" t="str">
         <x:v>ship</x:v>
@@ -45848,7 +45852,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C221" s="35" t="str">
-        <x:v>iceClassDraught</x:v>
+        <x:v>iceClassIa</x:v>
       </x:c>
       <x:c r="D221" s="35" t="str">
         <x:v>ship</x:v>
@@ -45868,7 +45872,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C222" s="35" t="str">
-        <x:v>iceClassIa</x:v>
+        <x:v>iceClassIaSuper</x:v>
       </x:c>
       <x:c r="D222" s="35" t="str">
         <x:v>ship</x:v>
@@ -45888,7 +45892,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C223" s="35" t="str">
-        <x:v>iceClassIaSuper</x:v>
+        <x:v>kilogramPerSquareMetreSquareSecondUnit</x:v>
       </x:c>
       <x:c r="D223" s="35" t="str">
         <x:v>ship</x:v>
@@ -45908,7 +45912,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C224" s="35" t="str">
-        <x:v>kilogramPerSquareMetreSquareSecondUnit</x:v>
+        <x:v>kilogramPerSquareSecondUnit</x:v>
       </x:c>
       <x:c r="D224" s="35" t="str">
         <x:v>ship</x:v>
@@ -45928,7 +45932,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C225" s="35" t="str">
-        <x:v>kilogramPerSquareSecondUnit</x:v>
+        <x:v>newtonPerMetreToPowerOnePointFiveUnit</x:v>
       </x:c>
       <x:c r="D225" s="35" t="str">
         <x:v>ship</x:v>
@@ -45948,7 +45952,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C226" s="35" t="str">
-        <x:v>newtonPerMetreToPowerOnePointFiveUnit</x:v>
+        <x:v>shipBreadth</x:v>
       </x:c>
       <x:c r="D226" s="35" t="str">
         <x:v>ship</x:v>
@@ -45968,7 +45972,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C227" s="35" t="str">
-        <x:v>shipBreadth</x:v>
+        <x:v>shipLength</x:v>
       </x:c>
       <x:c r="D227" s="35" t="str">
         <x:v>ship</x:v>
@@ -45982,20 +45986,18 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="38" t="str">
-        <x:v>TRF-027</x:v>
+        <x:v>TRF-028</x:v>
       </x:c>
       <x:c r="B228" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C228" s="35" t="str">
-        <x:v>shipLength</x:v>
+        <x:v>alternativeCalculationEvidence</x:v>
       </x:c>
       <x:c r="D228" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
-      <x:c r="E228" s="35" t="str">
-        <x:v>Require exactly one controlled iceClass before applicability branching; apply the Table 3-3 and clamped-geometry rules only to IA Super or IA ships with constructionStageDate before 1 September 2003.</x:v>
-      </x:c>
+      <x:c r="E228" s="35" t="str"/>
       <x:c r="F228" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -46008,7 +46010,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C229" s="35" t="str">
-        <x:v>alternativeCalculationEvidence</x:v>
+        <x:v>approvalRevocationStatus</x:v>
       </x:c>
       <x:c r="D229" s="35" t="str">
         <x:v>ship</x:v>
@@ -46026,7 +46028,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C230" s="35" t="str">
-        <x:v>approvalRevocationStatus</x:v>
+        <x:v>approvalStatus</x:v>
       </x:c>
       <x:c r="D230" s="35" t="str">
         <x:v>ship</x:v>
@@ -46044,7 +46046,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C231" s="35" t="str">
-        <x:v>approvalStatus</x:v>
+        <x:v>brashIceChannelResistanceRch</x:v>
       </x:c>
       <x:c r="D231" s="35" t="str">
         <x:v>ship</x:v>
@@ -46062,7 +46064,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C232" s="35" t="str">
-        <x:v>brashIceChannelResistanceRch</x:v>
+        <x:v>engineOutputCoefficientKe</x:v>
       </x:c>
       <x:c r="D232" s="35" t="str">
         <x:v>ship</x:v>
@@ -46080,7 +46082,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C233" s="35" t="str">
-        <x:v>engineOutputCoefficientKe</x:v>
+        <x:v>modelTestEvidence</x:v>
       </x:c>
       <x:c r="D233" s="35" t="str">
         <x:v>ship</x:v>
@@ -46098,7 +46100,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C234" s="35" t="str">
-        <x:v>modelTestEvidence</x:v>
+        <x:v>shipPerformanceExperienceEvidence</x:v>
       </x:c>
       <x:c r="D234" s="35" t="str">
         <x:v>ship</x:v>
@@ -46110,13 +46112,13 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="38" t="str">
-        <x:v>TRF-028</x:v>
+        <x:v>TRF-029</x:v>
       </x:c>
       <x:c r="B235" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C235" s="35" t="str">
-        <x:v>shipPerformanceExperienceEvidence</x:v>
+        <x:v>directAnalysisApprovalStatus</x:v>
       </x:c>
       <x:c r="D235" s="35" t="str">
         <x:v>ship</x:v>
@@ -46134,7 +46136,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C236" s="35" t="str">
-        <x:v>directAnalysisApprovalStatus</x:v>
+        <x:v>directAnalysisUsed</x:v>
       </x:c>
       <x:c r="D236" s="35" t="str">
         <x:v>ship</x:v>
@@ -46152,7 +46154,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C237" s="35" t="str">
-        <x:v>directAnalysisUsed</x:v>
+        <x:v>prescribedProcedureApplicability</x:v>
       </x:c>
       <x:c r="D237" s="35" t="str">
         <x:v>ship</x:v>
@@ -46170,7 +46172,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C238" s="35" t="str">
-        <x:v>prescribedProcedureApplicability</x:v>
+        <x:v>structuralArrangement</x:v>
       </x:c>
       <x:c r="D238" s="35" t="str">
         <x:v>ship</x:v>
@@ -46182,18 +46184,20 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="38" t="str">
-        <x:v>TRF-029</x:v>
+        <x:v>TRF-030</x:v>
       </x:c>
       <x:c r="B239" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C239" s="35" t="str">
-        <x:v>structuralArrangement</x:v>
+        <x:v>appliedIcePressure</x:v>
       </x:c>
       <x:c r="D239" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
-      <x:c r="E239" s="35" t="str"/>
+      <x:c r="E239" s="35" t="str">
+        <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
+      </x:c>
       <x:c r="F239" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -46206,10 +46210,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C240" s="35" t="str">
-        <x:v>appliedIcePressure</x:v>
+        <x:v>capacityMinimizingLoadPositionConfirmed</x:v>
       </x:c>
       <x:c r="D240" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="E240" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46226,7 +46230,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C241" s="35" t="str">
-        <x:v>capacityMinimizingLoadPositionConfirmed</x:v>
+        <x:v>combinedBendingAndShearEvaluated</x:v>
       </x:c>
       <x:c r="D241" s="35" t="str">
         <x:v>directAnalysisCase</x:v>
@@ -46246,10 +46250,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C242" s="35" t="str">
-        <x:v>combinedBendingAndShearEvaluated</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="D242" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E242" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46266,7 +46270,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C243" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
+        <x:v>halfLoadHeightBelowLowerIceWaterlinePosition</x:v>
       </x:c>
       <x:c r="D243" s="35" t="str">
         <x:v>ship</x:v>
@@ -46286,7 +46290,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C244" s="35" t="str">
-        <x:v>halfLoadHeightBelowLowerIceWaterlinePosition</x:v>
+        <x:v>hasDirectAnalysisCase</x:v>
       </x:c>
       <x:c r="D244" s="35" t="str">
         <x:v>ship</x:v>
@@ -46306,10 +46310,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C245" s="35" t="str">
-        <x:v>hasDirectAnalysisCase</x:v>
+        <x:v>horizontalLoadPosition</x:v>
       </x:c>
       <x:c r="D245" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="E245" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46326,7 +46330,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C246" s="35" t="str">
-        <x:v>horizontalLoadPosition</x:v>
+        <x:v>horizontalLoadPositionType</x:v>
       </x:c>
       <x:c r="D246" s="35" t="str">
         <x:v>directAnalysisCase</x:v>
@@ -46346,7 +46350,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C247" s="35" t="str">
-        <x:v>horizontalLoadPositionType</x:v>
+        <x:v>iceLoadAreaFactorCa</x:v>
       </x:c>
       <x:c r="D247" s="35" t="str">
         <x:v>directAnalysisCase</x:v>
@@ -46366,10 +46370,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C248" s="35" t="str">
-        <x:v>iceLoadAreaFactorCa</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D248" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E248" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46386,7 +46390,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C249" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>intermediateVerticalPosition</x:v>
       </x:c>
       <x:c r="D249" s="35" t="str">
         <x:v>ship</x:v>
@@ -46406,7 +46410,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C250" s="35" t="str">
-        <x:v>intermediateVerticalPosition</x:v>
+        <x:v>loadLengthDeterminedFromArrangement</x:v>
       </x:c>
       <x:c r="D250" s="35" t="str">
         <x:v>ship</x:v>
@@ -46426,7 +46430,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C251" s="35" t="str">
-        <x:v>loadLengthDeterminedFromArrangement</x:v>
+        <x:v>loadPatchApplicationLocation</x:v>
       </x:c>
       <x:c r="D251" s="35" t="str">
         <x:v>ship</x:v>
@@ -46446,7 +46450,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C252" s="35" t="str">
-        <x:v>loadPatchApplicationLocation</x:v>
+        <x:v>loadPatchHeight</x:v>
       </x:c>
       <x:c r="D252" s="35" t="str">
         <x:v>ship</x:v>
@@ -46466,10 +46470,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C253" s="35" t="str">
-        <x:v>loadPatchHeight</x:v>
+        <x:v>loadPatchLength</x:v>
       </x:c>
       <x:c r="D253" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="E253" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46486,7 +46490,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C254" s="35" t="str">
-        <x:v>loadPatchLength</x:v>
+        <x:v>lowerIceWaterlineReferencePosition</x:v>
       </x:c>
       <x:c r="D254" s="35" t="str">
         <x:v>directAnalysisCase</x:v>
@@ -46506,10 +46510,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C255" s="35" t="str">
-        <x:v>lowerIceWaterlineReferencePosition</x:v>
+        <x:v>midSpanOrSpacingCenteredPosition</x:v>
       </x:c>
       <x:c r="D255" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E255" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46526,7 +46530,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C256" s="35" t="str">
-        <x:v>midSpanOrSpacingCenteredPosition</x:v>
+        <x:v>otherHorizontalPosition</x:v>
       </x:c>
       <x:c r="D256" s="35" t="str">
         <x:v>ship</x:v>
@@ -46546,7 +46550,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C257" s="35" t="str">
-        <x:v>otherHorizontalPosition</x:v>
+        <x:v>spacing</x:v>
       </x:c>
       <x:c r="D257" s="35" t="str">
         <x:v>ship</x:v>
@@ -46566,7 +46570,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C258" s="35" t="str">
-        <x:v>spacing</x:v>
+        <x:v>span</x:v>
       </x:c>
       <x:c r="D258" s="35" t="str">
         <x:v>ship</x:v>
@@ -46586,7 +46590,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C259" s="35" t="str">
-        <x:v>span</x:v>
+        <x:v>upperIceWaterlineCenteredPosition</x:v>
       </x:c>
       <x:c r="D259" s="35" t="str">
         <x:v>ship</x:v>
@@ -46606,10 +46610,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C260" s="35" t="str">
-        <x:v>upperIceWaterlineCenteredPosition</x:v>
+        <x:v>upperIceWaterlineReferencePosition</x:v>
       </x:c>
       <x:c r="D260" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="E260" s="35" t="str">
         <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
@@ -46626,7 +46630,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C261" s="35" t="str">
-        <x:v>upperIceWaterlineReferencePosition</x:v>
+        <x:v>verticalLoadPosition</x:v>
       </x:c>
       <x:c r="D261" s="35" t="str">
         <x:v>directAnalysisCase</x:v>
@@ -46646,7 +46650,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C262" s="35" t="str">
-        <x:v>verticalLoadPosition</x:v>
+        <x:v>verticalLoadPositionType</x:v>
       </x:c>
       <x:c r="D262" s="35" t="str">
         <x:v>directAnalysisCase</x:v>
@@ -46660,20 +46664,18 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="38" t="str">
-        <x:v>TRF-030</x:v>
+        <x:v>TRF-031</x:v>
       </x:c>
       <x:c r="B263" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C263" s="35" t="str">
-        <x:v>verticalLoadPositionType</x:v>
+        <x:v>allowableShearStress</x:v>
       </x:c>
       <x:c r="D263" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
-      </x:c>
-      <x:c r="E263" s="35" t="str">
-        <x:v>Represent several vertical and horizontal directAnalysisCase nodes. Each case owns its position, combined bending/shear evidence, and capacity-minimizing evidence. | When load length is not determined from the arrangement, require several distinct directAnalysisCase nodes, each containing both its loadPatchLength and corresponding iceLoadAreaFactorCa; the shared case node is the canonical pairing structure.</x:v>
-      </x:c>
+        <x:v>ship</x:v>
+      </x:c>
+      <x:c r="E263" s="35" t="str"/>
       <x:c r="F263" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -46686,7 +46688,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C264" s="35" t="str">
-        <x:v>allowableShearStress</x:v>
+        <x:v>beamTheoryUsed</x:v>
       </x:c>
       <x:c r="D264" s="35" t="str">
         <x:v>ship</x:v>
@@ -46704,7 +46706,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C265" s="35" t="str">
-        <x:v>beamTheoryUsed</x:v>
+        <x:v>combinedBendingShearStress</x:v>
       </x:c>
       <x:c r="D265" s="35" t="str">
         <x:v>ship</x:v>
@@ -46722,7 +46724,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C266" s="35" t="str">
-        <x:v>combinedBendingShearStress</x:v>
+        <x:v>vonMisesYieldCriterion</x:v>
       </x:c>
       <x:c r="D266" s="35" t="str">
         <x:v>ship</x:v>
@@ -46740,7 +46742,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C267" s="35" t="str">
-        <x:v>vonMisesYieldCriterion</x:v>
+        <x:v>yieldPoint</x:v>
       </x:c>
       <x:c r="D267" s="35" t="str">
         <x:v>ship</x:v>
@@ -46758,7 +46760,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C268" s="35" t="str">
-        <x:v>yieldPoint</x:v>
+        <x:v>yieldShearStress</x:v>
       </x:c>
       <x:c r="D268" s="35" t="str">
         <x:v>ship</x:v>
@@ -46770,13 +46772,13 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="38" t="str">
-        <x:v>TRF-031</x:v>
+        <x:v>TRF-032</x:v>
       </x:c>
       <x:c r="B269" s="35" t="str">
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C269" s="35" t="str">
-        <x:v>yieldShearStress</x:v>
+        <x:v>classificationSocietyRequiredScantling</x:v>
       </x:c>
       <x:c r="D269" s="35" t="str">
         <x:v>ship</x:v>
@@ -46794,7 +46796,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C270" s="35" t="str">
-        <x:v>classificationSocietyRequiredScantling</x:v>
+        <x:v>iceStrengtheningStatus</x:v>
       </x:c>
       <x:c r="D270" s="35" t="str">
         <x:v>ship</x:v>
@@ -46812,7 +46814,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C271" s="35" t="str">
-        <x:v>iceStrengtheningStatus</x:v>
+        <x:v>regulationRequiredScantling</x:v>
       </x:c>
       <x:c r="D271" s="35" t="str">
         <x:v>ship</x:v>
@@ -46830,7 +46832,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C272" s="35" t="str">
-        <x:v>regulationRequiredScantling</x:v>
+        <x:v>selectedDesignScantling</x:v>
       </x:c>
       <x:c r="D272" s="35" t="str">
         <x:v>ship</x:v>
@@ -46842,16 +46844,16 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="38" t="str">
-        <x:v>TRF-032</x:v>
+        <x:v>TRF-034</x:v>
       </x:c>
       <x:c r="B273" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C273" s="35" t="str">
-        <x:v>selectedDesignScantling</x:v>
+        <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="D273" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="E273" s="35" t="str"/>
       <x:c r="F273" s="35" t="str">
@@ -46866,7 +46868,7 @@
         <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C274" s="35" t="str">
-        <x:v>effectiveMemberCrossSection</x:v>
+        <x:v>hasClassificationSocietySectionPropertyCalculationEvidence</x:v>
       </x:c>
       <x:c r="D274" s="35" t="str">
         <x:v>effectiveMemberCrossSection</x:v>
@@ -46884,10 +46886,10 @@
         <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C275" s="35" t="str">
-        <x:v>hasClassificationSocietySectionPropertyCalculationEvidence</x:v>
+        <x:v>hasEffectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="D275" s="35" t="str">
-        <x:v>effectiveMemberCrossSection</x:v>
+        <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="E275" s="35" t="str"/>
       <x:c r="F275" s="35" t="str">
@@ -46902,10 +46904,10 @@
         <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C276" s="35" t="str">
-        <x:v>hasEffectiveMemberCrossSection</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="D276" s="35" t="str">
-        <x:v>hullStructure</x:v>
+        <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="E276" s="35" t="str"/>
       <x:c r="F276" s="35" t="str">
@@ -46920,10 +46922,10 @@
         <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C277" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>memberNormalToPlating</x:v>
       </x:c>
       <x:c r="D277" s="35" t="str">
-        <x:v>effectiveMemberCrossSection</x:v>
+        <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="E277" s="35" t="str"/>
       <x:c r="F277" s="35" t="str">
@@ -46938,10 +46940,10 @@
         <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C278" s="35" t="str">
-        <x:v>memberNormalToPlating</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D278" s="35" t="str">
-        <x:v>hullStructure</x:v>
+        <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="E278" s="35" t="str"/>
       <x:c r="F278" s="35" t="str">
@@ -46956,7 +46958,7 @@
         <x:v>effectiveMemberCrossSection</x:v>
       </x:c>
       <x:c r="C279" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>shearArea</x:v>
       </x:c>
       <x:c r="D279" s="35" t="str">
         <x:v>effectiveMemberCrossSection</x:v>
@@ -46968,16 +46970,16 @@
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="38" t="str">
-        <x:v>TRF-034</x:v>
+        <x:v>TRF-035</x:v>
       </x:c>
       <x:c r="B280" s="35" t="str">
-        <x:v>effectiveMemberCrossSection</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="C280" s="35" t="str">
-        <x:v>shearArea</x:v>
+        <x:v>bowRegion</x:v>
       </x:c>
       <x:c r="D280" s="35" t="str">
-        <x:v>effectiveMemberCrossSection</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E280" s="35" t="str"/>
       <x:c r="F280" s="35" t="str">
@@ -46992,7 +46994,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C281" s="35" t="str">
-        <x:v>bowRegion</x:v>
+        <x:v>classificationSociety</x:v>
       </x:c>
       <x:c r="D281" s="35" t="str">
         <x:v>ship</x:v>
@@ -47010,7 +47012,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C282" s="35" t="str">
-        <x:v>classificationSociety</x:v>
+        <x:v>classificationSocietyRuleLength</x:v>
       </x:c>
       <x:c r="D282" s="35" t="str">
         <x:v>ship</x:v>
@@ -47028,7 +47030,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C283" s="35" t="str">
-        <x:v>classificationSocietyRuleLength</x:v>
+        <x:v>hullRegion</x:v>
       </x:c>
       <x:c r="D283" s="35" t="str">
         <x:v>ship</x:v>
@@ -47046,7 +47048,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C284" s="35" t="str">
-        <x:v>hullRegion</x:v>
+        <x:v>midbodyRegion</x:v>
       </x:c>
       <x:c r="D284" s="35" t="str">
         <x:v>ship</x:v>
@@ -47064,7 +47066,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C285" s="35" t="str">
-        <x:v>midbodyRegion</x:v>
+        <x:v>ruleLength</x:v>
       </x:c>
       <x:c r="D285" s="35" t="str">
         <x:v>ship</x:v>
@@ -47082,7 +47084,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C286" s="35" t="str">
-        <x:v>ruleLength</x:v>
+        <x:v>sternRegion</x:v>
       </x:c>
       <x:c r="D286" s="35" t="str">
         <x:v>ship</x:v>
@@ -47094,16 +47096,16 @@
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="38" t="str">
-        <x:v>TRF-035</x:v>
+        <x:v>TRF-036</x:v>
       </x:c>
       <x:c r="B287" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="C287" s="35" t="str">
-        <x:v>sternRegion</x:v>
+        <x:v>designIceLoadHeight</x:v>
       </x:c>
       <x:c r="D287" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="E287" s="35" t="str"/>
       <x:c r="F287" s="35" t="str">
@@ -47118,10 +47120,10 @@
         <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="C288" s="35" t="str">
-        <x:v>designIceLoadHeight</x:v>
+        <x:v>hasIceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="D288" s="35" t="str">
-        <x:v>iceClassDesignParameterSet</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E288" s="35" t="str"/>
       <x:c r="F288" s="35" t="str">
@@ -47136,7 +47138,7 @@
         <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="C289" s="35" t="str">
-        <x:v>hasIceClassDesignParameterSet</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D289" s="35" t="str">
         <x:v>ship</x:v>
@@ -47154,10 +47156,10 @@
         <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="C290" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="D290" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="E290" s="35" t="str"/>
       <x:c r="F290" s="35" t="str">
@@ -47172,7 +47174,7 @@
         <x:v>iceClassDesignParameterSet</x:v>
       </x:c>
       <x:c r="C291" s="35" t="str">
-        <x:v>iceClassDesignParameterSet</x:v>
+        <x:v>levelIceThickness</x:v>
       </x:c>
       <x:c r="D291" s="35" t="str">
         <x:v>iceClassDesignParameterSet</x:v>
@@ -47184,18 +47186,20 @@
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="38" t="str">
-        <x:v>TRF-036</x:v>
+        <x:v>TRF-037</x:v>
       </x:c>
       <x:c r="B292" s="35" t="str">
-        <x:v>iceClassDesignParameterSet</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="C292" s="35" t="str">
-        <x:v>levelIceThickness</x:v>
+        <x:v>continuousPropulsionPowerAvailableInIce</x:v>
       </x:c>
       <x:c r="D292" s="35" t="str">
-        <x:v>iceClassDesignParameterSet</x:v>
-      </x:c>
-      <x:c r="E292" s="35" t="str"/>
+        <x:v>ship</x:v>
+      </x:c>
+      <x:c r="E292" s="35" t="str">
+        <x:v>Compute rawCd=(a*k+b)/1000 and validate shipSizeEngineOutputFactorCd against IF(rawCd &gt; 1, 1, rawCd); the maximum is a cap, not a rejection of raw values above 1. | Validate icePressure = shipSizeEngineOutputFactorCd * iceClassFactorCp * iceLoadAreaFactorCa * nominalIcePressureP0; iceLoadAreaFactorCa is owned by directAnalysisCase and is reached from ship with hasDirectAnalysisCase.</x:v>
+      </x:c>
       <x:c r="F292" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -47208,7 +47212,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C293" s="35" t="str">
-        <x:v>continuousPropulsionPowerAvailableInIce</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="D293" s="35" t="str">
         <x:v>ship</x:v>
@@ -47228,7 +47232,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C294" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
+        <x:v>displacementAtMaximumIceClassDraught</x:v>
       </x:c>
       <x:c r="D294" s="35" t="str">
         <x:v>ship</x:v>
@@ -47248,7 +47252,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C295" s="35" t="str">
-        <x:v>displacementAtMaximumIceClassDraught</x:v>
+        <x:v>hasDirectAnalysisCase</x:v>
       </x:c>
       <x:c r="D295" s="35" t="str">
         <x:v>ship</x:v>
@@ -47268,7 +47272,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C296" s="35" t="str">
-        <x:v>hasDirectAnalysisCase</x:v>
+        <x:v>hullRegion</x:v>
       </x:c>
       <x:c r="D296" s="35" t="str">
         <x:v>ship</x:v>
@@ -47288,7 +47292,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C297" s="35" t="str">
-        <x:v>hullRegion</x:v>
+        <x:v>iceClassFactorCp</x:v>
       </x:c>
       <x:c r="D297" s="35" t="str">
         <x:v>ship</x:v>
@@ -47308,10 +47312,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C298" s="35" t="str">
-        <x:v>iceClassFactorCp</x:v>
+        <x:v>iceLoadAreaFactorCa</x:v>
       </x:c>
       <x:c r="D298" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>directAnalysisCase</x:v>
       </x:c>
       <x:c r="E298" s="35" t="str">
         <x:v>Compute rawCd=(a*k+b)/1000 and validate shipSizeEngineOutputFactorCd against IF(rawCd &gt; 1, 1, rawCd); the maximum is a cap, not a rejection of raw values above 1. | Validate icePressure = shipSizeEngineOutputFactorCd * iceClassFactorCp * iceLoadAreaFactorCa * nominalIcePressureP0; iceLoadAreaFactorCa is owned by directAnalysisCase and is reached from ship with hasDirectAnalysisCase.</x:v>
@@ -47328,10 +47332,10 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C299" s="35" t="str">
-        <x:v>iceLoadAreaFactorCa</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D299" s="35" t="str">
-        <x:v>directAnalysisCase</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E299" s="35" t="str">
         <x:v>Compute rawCd=(a*k+b)/1000 and validate shipSizeEngineOutputFactorCd against IF(rawCd &gt; 1, 1, rawCd); the maximum is a cap, not a rejection of raw values above 1. | Validate icePressure = shipSizeEngineOutputFactorCd * iceClassFactorCp * iceLoadAreaFactorCa * nominalIcePressureP0; iceLoadAreaFactorCa is owned by directAnalysisCase and is reached from ship with hasDirectAnalysisCase.</x:v>
@@ -47348,7 +47352,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C300" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>nominalIcePressureP0</x:v>
       </x:c>
       <x:c r="D300" s="35" t="str">
         <x:v>ship</x:v>
@@ -47368,7 +47372,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C301" s="35" t="str">
-        <x:v>nominalIcePressureP0</x:v>
+        <x:v>shipSizeEngineOutputCoefficientA</x:v>
       </x:c>
       <x:c r="D301" s="35" t="str">
         <x:v>ship</x:v>
@@ -47388,7 +47392,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C302" s="35" t="str">
-        <x:v>shipSizeEngineOutputCoefficientA</x:v>
+        <x:v>shipSizeEngineOutputCoefficientB</x:v>
       </x:c>
       <x:c r="D302" s="35" t="str">
         <x:v>ship</x:v>
@@ -47408,7 +47412,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C303" s="35" t="str">
-        <x:v>shipSizeEngineOutputCoefficientB</x:v>
+        <x:v>shipSizeEngineOutputCoefficientK</x:v>
       </x:c>
       <x:c r="D303" s="35" t="str">
         <x:v>ship</x:v>
@@ -47428,7 +47432,7 @@
         <x:v>ship</x:v>
       </x:c>
       <x:c r="C304" s="35" t="str">
-        <x:v>shipSizeEngineOutputCoefficientK</x:v>
+        <x:v>shipSizeEngineOutputFactorCd</x:v>
       </x:c>
       <x:c r="D304" s="35" t="str">
         <x:v>ship</x:v>
@@ -47442,19 +47446,19 @@
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="38" t="str">
-        <x:v>TRF-037</x:v>
+        <x:v>TRF-041</x:v>
       </x:c>
       <x:c r="B305" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>plating</x:v>
       </x:c>
       <x:c r="C305" s="35" t="str">
-        <x:v>shipSizeEngineOutputFactorCd</x:v>
+        <x:v>corrosionAbrasionAddition</x:v>
       </x:c>
       <x:c r="D305" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>plating</x:v>
       </x:c>
       <x:c r="E305" s="35" t="str">
-        <x:v>Compute rawCd=(a*k+b)/1000 and validate shipSizeEngineOutputFactorCd against IF(rawCd &gt; 1, 1, rawCd); the maximum is a cap, not a rejection of raw values above 1. | Validate icePressure = shipSizeEngineOutputFactorCd * iceClassFactorCp * iceLoadAreaFactorCa * nominalIcePressureP0; iceLoadAreaFactorCa is owned by directAnalysisCase and is reached from ship with hasDirectAnalysisCase.</x:v>
+        <x:v>Use the applicable transverse or longitudinal plating formula and reject missing operands; do not target generic benchmarkEntity.</x:v>
       </x:c>
       <x:c r="F305" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
@@ -47468,7 +47472,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C306" s="35" t="str">
-        <x:v>corrosionAbrasionAddition</x:v>
+        <x:v>hullStructuralSteelGrade</x:v>
       </x:c>
       <x:c r="D306" s="35" t="str">
         <x:v>plating</x:v>
@@ -47488,7 +47492,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C307" s="35" t="str">
-        <x:v>hullStructuralSteelGrade</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D307" s="35" t="str">
         <x:v>plating</x:v>
@@ -47508,7 +47512,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C308" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>longitudinalFramingOrientation</x:v>
       </x:c>
       <x:c r="D308" s="35" t="str">
         <x:v>plating</x:v>
@@ -47528,7 +47532,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C309" s="35" t="str">
-        <x:v>longitudinalFramingOrientation</x:v>
+        <x:v>longitudinalPlatingFactorF2</x:v>
       </x:c>
       <x:c r="D309" s="35" t="str">
         <x:v>plating</x:v>
@@ -47548,7 +47552,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C310" s="35" t="str">
-        <x:v>longitudinalPlatingFactorF2</x:v>
+        <x:v>platingFramingOrientation</x:v>
       </x:c>
       <x:c r="D310" s="35" t="str">
         <x:v>plating</x:v>
@@ -47568,7 +47572,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C311" s="35" t="str">
-        <x:v>platingFramingOrientation</x:v>
+        <x:v>platingPressure</x:v>
       </x:c>
       <x:c r="D311" s="35" t="str">
         <x:v>plating</x:v>
@@ -47588,7 +47592,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C312" s="35" t="str">
-        <x:v>platingPressure</x:v>
+        <x:v>requiredShellPlatingThickness</x:v>
       </x:c>
       <x:c r="D312" s="35" t="str">
         <x:v>plating</x:v>
@@ -47608,7 +47612,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C313" s="35" t="str">
-        <x:v>requiredShellPlatingThickness</x:v>
+        <x:v>spacing</x:v>
       </x:c>
       <x:c r="D313" s="35" t="str">
         <x:v>plating</x:v>
@@ -47628,7 +47632,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C314" s="35" t="str">
-        <x:v>spacing</x:v>
+        <x:v>transverseFramingOrientation</x:v>
       </x:c>
       <x:c r="D314" s="35" t="str">
         <x:v>plating</x:v>
@@ -47648,7 +47652,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C315" s="35" t="str">
-        <x:v>transverseFramingOrientation</x:v>
+        <x:v>transversePlatingFactorF1</x:v>
       </x:c>
       <x:c r="D315" s="35" t="str">
         <x:v>plating</x:v>
@@ -47668,7 +47672,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C316" s="35" t="str">
-        <x:v>transversePlatingFactorF1</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D316" s="35" t="str">
         <x:v>plating</x:v>
@@ -47682,19 +47686,19 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="38" t="str">
-        <x:v>TRF-041</x:v>
+        <x:v>TRF-042</x:v>
       </x:c>
       <x:c r="B317" s="35" t="str">
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C317" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>corrosionAbrasionAddition</x:v>
       </x:c>
       <x:c r="D317" s="35" t="str">
         <x:v>plating</x:v>
       </x:c>
       <x:c r="E317" s="35" t="str">
-        <x:v>Use the applicable transverse or longitudinal plating formula and reject missing operands; do not target generic benchmarkEntity.</x:v>
+        <x:v>Use tolerance max(1e-6*ABS(expected),1e-12), not the sum of relative and absolute tolerances, for derived f2 comparison. | Constrain materialApprovalStatus to the canonical evidenceState range when a lower corrosion addition is justified by approved maintained coating evidence.</x:v>
       </x:c>
       <x:c r="F317" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
@@ -47708,7 +47712,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C318" s="35" t="str">
-        <x:v>corrosionAbrasionAddition</x:v>
+        <x:v>designIceLoadHeight</x:v>
       </x:c>
       <x:c r="D318" s="35" t="str">
         <x:v>plating</x:v>
@@ -47728,7 +47732,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C319" s="35" t="str">
-        <x:v>designIceLoadHeight</x:v>
+        <x:v>hullStructuralSteelGrade</x:v>
       </x:c>
       <x:c r="D319" s="35" t="str">
         <x:v>plating</x:v>
@@ -47748,7 +47752,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C320" s="35" t="str">
-        <x:v>hullStructuralSteelGrade</x:v>
+        <x:v>longitudinalPlatingFactorF2</x:v>
       </x:c>
       <x:c r="D320" s="35" t="str">
         <x:v>plating</x:v>
@@ -47768,7 +47772,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C321" s="35" t="str">
-        <x:v>longitudinalPlatingFactorF2</x:v>
+        <x:v>materialApprovalStatus</x:v>
       </x:c>
       <x:c r="D321" s="35" t="str">
         <x:v>plating</x:v>
@@ -47788,7 +47792,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C322" s="35" t="str">
-        <x:v>materialApprovalStatus</x:v>
+        <x:v>plating</x:v>
       </x:c>
       <x:c r="D322" s="35" t="str">
         <x:v>plating</x:v>
@@ -47808,7 +47812,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C323" s="35" t="str">
-        <x:v>plating</x:v>
+        <x:v>requiredShellPlatingThickness</x:v>
       </x:c>
       <x:c r="D323" s="35" t="str">
         <x:v>plating</x:v>
@@ -47828,7 +47832,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C324" s="35" t="str">
-        <x:v>requiredShellPlatingThickness</x:v>
+        <x:v>spacing</x:v>
       </x:c>
       <x:c r="D324" s="35" t="str">
         <x:v>plating</x:v>
@@ -47848,7 +47852,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C325" s="35" t="str">
-        <x:v>spacing</x:v>
+        <x:v>specialSurfaceCoatingMaintained</x:v>
       </x:c>
       <x:c r="D325" s="35" t="str">
         <x:v>plating</x:v>
@@ -47868,7 +47872,7 @@
         <x:v>plating</x:v>
       </x:c>
       <x:c r="C326" s="35" t="str">
-        <x:v>specialSurfaceCoatingMaintained</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D326" s="35" t="str">
         <x:v>plating</x:v>
@@ -47882,19 +47886,19 @@
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="38" t="str">
-        <x:v>TRF-042</x:v>
+        <x:v>TRF-043</x:v>
       </x:c>
       <x:c r="B327" s="35" t="str">
-        <x:v>plating</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="C327" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>extensionBeyondAdjacentDeckOrTankBoundary</x:v>
       </x:c>
       <x:c r="D327" s="35" t="str">
-        <x:v>plating</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E327" s="35" t="str">
-        <x:v>Use tolerance max(1e-6*ABS(expected),1e-12), not the sum of relative and absolute tolerances, for derived f2 comparison. | Constrain materialApprovalStatus to the canonical evidenceState range when a lower corrosion addition is justified by approved maintained coating evidence.</x:v>
+        <x:v>Apply Table 4-6 minima by default and model the &lt;=250 mm termination allowance only as an explicit exception.</x:v>
       </x:c>
       <x:c r="F327" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
@@ -47908,7 +47912,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C328" s="35" t="str">
-        <x:v>extensionBeyondAdjacentDeckOrTankBoundary</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="D328" s="35" t="str">
         <x:v>frame</x:v>
@@ -47928,7 +47932,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C329" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>framingIceStrengtheningAboveUpperIceWaterline</x:v>
       </x:c>
       <x:c r="D329" s="35" t="str">
         <x:v>frame</x:v>
@@ -47948,7 +47952,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C330" s="35" t="str">
-        <x:v>framingIceStrengtheningAboveUpperIceWaterline</x:v>
+        <x:v>framingIceStrengtheningBelowLowerIceWaterline</x:v>
       </x:c>
       <x:c r="D330" s="35" t="str">
         <x:v>frame</x:v>
@@ -47968,7 +47972,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C331" s="35" t="str">
-        <x:v>framingIceStrengtheningBelowLowerIceWaterline</x:v>
+        <x:v>hullRegion</x:v>
       </x:c>
       <x:c r="D331" s="35" t="str">
         <x:v>frame</x:v>
@@ -47988,7 +47992,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C332" s="35" t="str">
-        <x:v>hullRegion</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D332" s="35" t="str">
         <x:v>frame</x:v>
@@ -48008,7 +48012,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C333" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>iceStrengtheningTerminationAtAdjacentBoundaryPermitted</x:v>
       </x:c>
       <x:c r="D333" s="35" t="str">
         <x:v>frame</x:v>
@@ -48028,7 +48032,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C334" s="35" t="str">
-        <x:v>iceStrengtheningTerminationAtAdjacentBoundaryPermitted</x:v>
+        <x:v>reachesTankTopOrBelowFloorTop</x:v>
       </x:c>
       <x:c r="D334" s="35" t="str">
         <x:v>frame</x:v>
@@ -48048,7 +48052,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C335" s="35" t="str">
-        <x:v>reachesTankTopOrBelowFloorTop</x:v>
+        <x:v>reachesUpperBowIceBeltTop</x:v>
       </x:c>
       <x:c r="D335" s="35" t="str">
         <x:v>frame</x:v>
@@ -48068,7 +48072,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C336" s="35" t="str">
-        <x:v>reachesUpperBowIceBeltTop</x:v>
+        <x:v>upperBowIceBeltRequired</x:v>
       </x:c>
       <x:c r="D336" s="35" t="str">
         <x:v>frame</x:v>
@@ -48082,20 +48086,18 @@
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="38" t="str">
-        <x:v>TRF-043</x:v>
+        <x:v>TRF-044</x:v>
       </x:c>
       <x:c r="B337" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C337" s="35" t="str">
-        <x:v>upperBowIceBeltRequired</x:v>
+        <x:v>designIceLoadHeight</x:v>
       </x:c>
       <x:c r="D337" s="35" t="str">
-        <x:v>frame</x:v>
-      </x:c>
-      <x:c r="E337" s="35" t="str">
-        <x:v>Apply Table 4-6 minima by default and model the &lt;=250 mm termination allowance only as an explicit exception.</x:v>
-      </x:c>
+        <x:v>transverseFrame</x:v>
+      </x:c>
+      <x:c r="E337" s="35" t="str"/>
       <x:c r="F337" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -48108,7 +48110,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C338" s="35" t="str">
-        <x:v>designIceLoadHeight</x:v>
+        <x:v>effectiveFrameSpan</x:v>
       </x:c>
       <x:c r="D338" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48126,7 +48128,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C339" s="35" t="str">
-        <x:v>effectiveFrameSpan</x:v>
+        <x:v>frameBoundaryConditionFactorM0</x:v>
       </x:c>
       <x:c r="D339" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48144,7 +48146,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C340" s="35" t="str">
-        <x:v>frameBoundaryConditionFactorM0</x:v>
+        <x:v>frameBoundaryConditionType</x:v>
       </x:c>
       <x:c r="D340" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48162,7 +48164,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C341" s="35" t="str">
-        <x:v>frameBoundaryConditionType</x:v>
+        <x:v>frameMomentFactorMt</x:v>
       </x:c>
       <x:c r="D341" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48180,7 +48182,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C342" s="35" t="str">
-        <x:v>frameMomentFactorMt</x:v>
+        <x:v>frameShearDistributionFactorF3</x:v>
       </x:c>
       <x:c r="D342" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48198,7 +48200,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C343" s="35" t="str">
-        <x:v>frameShearDistributionFactorF3</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D343" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48216,7 +48218,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C344" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>intermediateTransverseFrame</x:v>
       </x:c>
       <x:c r="D344" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48234,7 +48236,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C345" s="35" t="str">
-        <x:v>intermediateTransverseFrame</x:v>
+        <x:v>mainTransverseFrame</x:v>
       </x:c>
       <x:c r="D345" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48252,7 +48254,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C346" s="35" t="str">
-        <x:v>mainTransverseFrame</x:v>
+        <x:v>requiredShearArea</x:v>
       </x:c>
       <x:c r="D346" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48270,7 +48272,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C347" s="35" t="str">
-        <x:v>requiredShearArea</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D347" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48288,7 +48290,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C348" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>spacing</x:v>
       </x:c>
       <x:c r="D348" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48306,7 +48308,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C349" s="35" t="str">
-        <x:v>spacing</x:v>
+        <x:v>span</x:v>
       </x:c>
       <x:c r="D349" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48324,7 +48326,7 @@
         <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="C350" s="35" t="str">
-        <x:v>span</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D350" s="35" t="str">
         <x:v>transverseFrame</x:v>
@@ -48336,16 +48338,16 @@
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="38" t="str">
-        <x:v>TRF-044</x:v>
+        <x:v>TRF-045</x:v>
       </x:c>
       <x:c r="B351" s="35" t="str">
-        <x:v>transverseFrame</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="C351" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>frameSpanWithinIceStrengtheningZone</x:v>
       </x:c>
       <x:c r="D351" s="35" t="str">
-        <x:v>transverseFrame</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E351" s="35" t="str"/>
       <x:c r="F351" s="35" t="str">
@@ -48360,7 +48362,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C352" s="35" t="str">
-        <x:v>frameSpanWithinIceStrengtheningZone</x:v>
+        <x:v>ordinaryFrameScantlingsUsed</x:v>
       </x:c>
       <x:c r="D352" s="35" t="str">
         <x:v>frame</x:v>
@@ -48378,7 +48380,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C353" s="35" t="str">
-        <x:v>ordinaryFrameScantlingsUsed</x:v>
+        <x:v>span</x:v>
       </x:c>
       <x:c r="D353" s="35" t="str">
         <x:v>frame</x:v>
@@ -48390,18 +48392,20 @@
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="38" t="str">
-        <x:v>TRF-045</x:v>
+        <x:v>TRF-046</x:v>
       </x:c>
       <x:c r="B354" s="35" t="str">
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C354" s="35" t="str">
-        <x:v>span</x:v>
+        <x:v>connectsToAdjacentMainFrame</x:v>
       </x:c>
       <x:c r="D354" s="35" t="str">
-        <x:v>frame</x:v>
-      </x:c>
-      <x:c r="E354" s="35" t="str"/>
+        <x:v>horizontalConnectionMember</x:v>
+      </x:c>
+      <x:c r="E354" s="35" t="str">
+        <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
+      </x:c>
       <x:c r="F354" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -48414,10 +48418,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C355" s="35" t="str">
-        <x:v>connectsToAdjacentMainFrame</x:v>
+        <x:v>deckStructure</x:v>
       </x:c>
       <x:c r="D355" s="35" t="str">
-        <x:v>horizontalConnectionMember</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E355" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48434,7 +48438,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C356" s="35" t="str">
-        <x:v>deckStructure</x:v>
+        <x:v>frameStrengthenedPart</x:v>
       </x:c>
       <x:c r="D356" s="35" t="str">
         <x:v>frame</x:v>
@@ -48454,10 +48458,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C357" s="35" t="str">
-        <x:v>frameStrengthenedPart</x:v>
+        <x:v>hasAttachedSupportingStructure</x:v>
       </x:c>
       <x:c r="D357" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameEnd</x:v>
       </x:c>
       <x:c r="E357" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48474,7 +48478,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C358" s="35" t="str">
-        <x:v>hasAttachedSupportingStructure</x:v>
+        <x:v>hasHorizontalConnectionMember</x:v>
       </x:c>
       <x:c r="D358" s="35" t="str">
         <x:v>frameEnd</x:v>
@@ -48494,10 +48498,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C359" s="35" t="str">
-        <x:v>hasHorizontalConnectionMember</x:v>
+        <x:v>hasStrengthenedPart</x:v>
       </x:c>
       <x:c r="D359" s="35" t="str">
-        <x:v>frameEnd</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E359" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48514,10 +48518,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C360" s="35" t="str">
-        <x:v>hasStrengthenedPart</x:v>
+        <x:v>hasTerminationAboveSupportingStructure</x:v>
       </x:c>
       <x:c r="D360" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameEnd</x:v>
       </x:c>
       <x:c r="E360" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48534,10 +48538,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C361" s="35" t="str">
-        <x:v>hasTerminationAboveSupportingStructure</x:v>
+        <x:v>hasUpperEnd</x:v>
       </x:c>
       <x:c r="D361" s="35" t="str">
-        <x:v>frameEnd</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E361" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48554,7 +48558,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C362" s="35" t="str">
-        <x:v>hasUpperEnd</x:v>
+        <x:v>horizontalConnectionMember</x:v>
       </x:c>
       <x:c r="D362" s="35" t="str">
         <x:v>frame</x:v>
@@ -48574,7 +48578,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C363" s="35" t="str">
-        <x:v>horizontalConnectionMember</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="D363" s="35" t="str">
         <x:v>frame</x:v>
@@ -48594,7 +48598,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C364" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>intermediateIceFrame</x:v>
       </x:c>
       <x:c r="D364" s="35" t="str">
         <x:v>frame</x:v>
@@ -48614,7 +48618,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C365" s="35" t="str">
-        <x:v>intermediateIceFrame</x:v>
+        <x:v>mainFrame</x:v>
       </x:c>
       <x:c r="D365" s="35" t="str">
         <x:v>frame</x:v>
@@ -48634,10 +48638,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C366" s="35" t="str">
-        <x:v>mainFrame</x:v>
+        <x:v>ordinaryFrameScantlingsUsed</x:v>
       </x:c>
       <x:c r="D366" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameStrengthenedPart</x:v>
       </x:c>
       <x:c r="E366" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48654,10 +48658,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C367" s="35" t="str">
-        <x:v>ordinaryFrameScantlingsUsed</x:v>
+        <x:v>sameScantlingsAsMainFrame</x:v>
       </x:c>
       <x:c r="D367" s="35" t="str">
-        <x:v>frameStrengthenedPart</x:v>
+        <x:v>horizontalConnectionMember</x:v>
       </x:c>
       <x:c r="E367" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48674,10 +48678,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C368" s="35" t="str">
-        <x:v>sameScantlingsAsMainFrame</x:v>
+        <x:v>supportingStructure</x:v>
       </x:c>
       <x:c r="D368" s="35" t="str">
-        <x:v>horizontalConnectionMember</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E368" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48694,10 +48698,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C369" s="35" t="str">
+        <x:v>supportingStructureAtOrAboveIceBeltUpperLimit</x:v>
+      </x:c>
+      <x:c r="D369" s="35" t="str">
         <x:v>supportingStructure</x:v>
-      </x:c>
-      <x:c r="D369" s="35" t="str">
-        <x:v>frame</x:v>
       </x:c>
       <x:c r="E369" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48714,10 +48718,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C370" s="35" t="str">
-        <x:v>supportingStructureAtOrAboveIceBeltUpperLimit</x:v>
+        <x:v>tankBoundaryPlating</x:v>
       </x:c>
       <x:c r="D370" s="35" t="str">
-        <x:v>supportingStructure</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E370" s="35" t="str">
         <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
@@ -48734,7 +48738,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C371" s="35" t="str">
-        <x:v>tankBoundaryPlating</x:v>
+        <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="D371" s="35" t="str">
         <x:v>frame</x:v>
@@ -48748,20 +48752,18 @@
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="38" t="str">
-        <x:v>TRF-046</x:v>
+        <x:v>TRF-047</x:v>
       </x:c>
       <x:c r="B372" s="35" t="str">
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C372" s="35" t="str">
-        <x:v>transverseFrame</x:v>
+        <x:v>connectsToAdjacentMainFrame</x:v>
       </x:c>
       <x:c r="D372" s="35" t="str">
         <x:v>frame</x:v>
       </x:c>
-      <x:c r="E372" s="35" t="str">
-        <x:v>Require the strengthened upper end to attach to an eligible supporting structure. The at-or-above-ice-belt condition qualifies only the ordinary-scantlings and intermediate-frame horizontal-member permissions; it is not an unconditional attachment requirement.</x:v>
-      </x:c>
+      <x:c r="E372" s="35" t="str"/>
       <x:c r="F372" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -48774,7 +48776,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C373" s="35" t="str">
-        <x:v>connectsToAdjacentMainFrame</x:v>
+        <x:v>deckStructure</x:v>
       </x:c>
       <x:c r="D373" s="35" t="str">
         <x:v>frame</x:v>
@@ -48792,7 +48794,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C374" s="35" t="str">
-        <x:v>deckStructure</x:v>
+        <x:v>frameStrengthenedPart</x:v>
       </x:c>
       <x:c r="D374" s="35" t="str">
         <x:v>frame</x:v>
@@ -48810,7 +48812,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C375" s="35" t="str">
-        <x:v>frameStrengthenedPart</x:v>
+        <x:v>hasAttachedSupportingStructure</x:v>
       </x:c>
       <x:c r="D375" s="35" t="str">
         <x:v>frame</x:v>
@@ -48828,10 +48830,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C376" s="35" t="str">
-        <x:v>hasAttachedSupportingStructure</x:v>
+        <x:v>hasHorizontalConnectionMember</x:v>
       </x:c>
       <x:c r="D376" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameEnd</x:v>
       </x:c>
       <x:c r="E376" s="35" t="str"/>
       <x:c r="F376" s="35" t="str">
@@ -48846,10 +48848,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C377" s="35" t="str">
-        <x:v>hasHorizontalConnectionMember</x:v>
+        <x:v>hasLowerEnd</x:v>
       </x:c>
       <x:c r="D377" s="35" t="str">
-        <x:v>frameEnd</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E377" s="35" t="str"/>
       <x:c r="F377" s="35" t="str">
@@ -48864,7 +48866,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C378" s="35" t="str">
-        <x:v>hasLowerEnd</x:v>
+        <x:v>hasStrengthenedPart</x:v>
       </x:c>
       <x:c r="D378" s="35" t="str">
         <x:v>frame</x:v>
@@ -48882,7 +48884,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C379" s="35" t="str">
-        <x:v>hasStrengthenedPart</x:v>
+        <x:v>hasTerminationBelowSupportingStructure</x:v>
       </x:c>
       <x:c r="D379" s="35" t="str">
         <x:v>frame</x:v>
@@ -48900,7 +48902,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C380" s="35" t="str">
-        <x:v>hasTerminationBelowSupportingStructure</x:v>
+        <x:v>horizontalConnectionMember</x:v>
       </x:c>
       <x:c r="D380" s="35" t="str">
         <x:v>frame</x:v>
@@ -48918,7 +48920,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C381" s="35" t="str">
-        <x:v>horizontalConnectionMember</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="D381" s="35" t="str">
         <x:v>frame</x:v>
@@ -48936,7 +48938,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C382" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>intermediateIceFrame</x:v>
       </x:c>
       <x:c r="D382" s="35" t="str">
         <x:v>frame</x:v>
@@ -48954,7 +48956,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C383" s="35" t="str">
-        <x:v>intermediateIceFrame</x:v>
+        <x:v>mainFrame</x:v>
       </x:c>
       <x:c r="D383" s="35" t="str">
         <x:v>frame</x:v>
@@ -48972,7 +48974,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C384" s="35" t="str">
-        <x:v>mainFrame</x:v>
+        <x:v>mainFrameBelowIceBeltStrengthened</x:v>
       </x:c>
       <x:c r="D384" s="35" t="str">
         <x:v>frame</x:v>
@@ -48990,7 +48992,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C385" s="35" t="str">
-        <x:v>mainFrameBelowIceBeltStrengthened</x:v>
+        <x:v>ordinaryFrameScantlingsUsed</x:v>
       </x:c>
       <x:c r="D385" s="35" t="str">
         <x:v>frame</x:v>
@@ -49008,7 +49010,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C386" s="35" t="str">
-        <x:v>ordinaryFrameScantlingsUsed</x:v>
+        <x:v>sameScantlingsAsMainFrame</x:v>
       </x:c>
       <x:c r="D386" s="35" t="str">
         <x:v>frame</x:v>
@@ -49026,7 +49028,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C387" s="35" t="str">
-        <x:v>sameScantlingsAsMainFrame</x:v>
+        <x:v>supportingStructure</x:v>
       </x:c>
       <x:c r="D387" s="35" t="str">
         <x:v>frame</x:v>
@@ -49044,7 +49046,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C388" s="35" t="str">
-        <x:v>supportingStructure</x:v>
+        <x:v>supportingStructureAtOrBelowIceBeltLowerLimit</x:v>
       </x:c>
       <x:c r="D388" s="35" t="str">
         <x:v>frame</x:v>
@@ -49062,7 +49064,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C389" s="35" t="str">
-        <x:v>supportingStructureAtOrBelowIceBeltLowerLimit</x:v>
+        <x:v>tankBoundaryPlating</x:v>
       </x:c>
       <x:c r="D389" s="35" t="str">
         <x:v>frame</x:v>
@@ -49080,7 +49082,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C390" s="35" t="str">
-        <x:v>tankBoundaryPlating</x:v>
+        <x:v>tankTop</x:v>
       </x:c>
       <x:c r="D390" s="35" t="str">
         <x:v>frame</x:v>
@@ -49098,7 +49100,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C391" s="35" t="str">
-        <x:v>tankTop</x:v>
+        <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="D391" s="35" t="str">
         <x:v>frame</x:v>
@@ -49110,16 +49112,16 @@
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="38" t="str">
-        <x:v>TRF-047</x:v>
+        <x:v>TRF-048</x:v>
       </x:c>
       <x:c r="B392" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C392" s="35" t="str">
-        <x:v>transverseFrame</x:v>
+        <x:v>actualFrameShearArea</x:v>
       </x:c>
       <x:c r="D392" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="E392" s="35" t="str"/>
       <x:c r="F392" s="35" t="str">
@@ -49134,7 +49136,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C393" s="35" t="str">
-        <x:v>actualFrameShearArea</x:v>
+        <x:v>bracketArea</x:v>
       </x:c>
       <x:c r="D393" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49152,7 +49154,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C394" s="35" t="str">
-        <x:v>bracketArea</x:v>
+        <x:v>connectionBracket</x:v>
       </x:c>
       <x:c r="D394" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49170,7 +49172,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C395" s="35" t="str">
-        <x:v>connectionBracket</x:v>
+        <x:v>designIceLoadHeight</x:v>
       </x:c>
       <x:c r="D395" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49188,7 +49190,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C396" s="35" t="str">
-        <x:v>designIceLoadHeight</x:v>
+        <x:v>frameBoundaryConditionEvidence</x:v>
       </x:c>
       <x:c r="D396" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49206,7 +49208,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C397" s="35" t="str">
-        <x:v>frameBoundaryConditionEvidence</x:v>
+        <x:v>frameMomentFactorM</x:v>
       </x:c>
       <x:c r="D397" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49224,7 +49226,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C398" s="35" t="str">
-        <x:v>frameMomentFactorM</x:v>
+        <x:v>grossFrameShearArea</x:v>
       </x:c>
       <x:c r="D398" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49242,7 +49244,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C399" s="35" t="str">
-        <x:v>grossFrameShearArea</x:v>
+        <x:v>hasFrameBoundaryConditionEvidence</x:v>
       </x:c>
       <x:c r="D399" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49260,7 +49262,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C400" s="35" t="str">
-        <x:v>hasFrameBoundaryConditionEvidence</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D400" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49278,7 +49280,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C401" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="D401" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49296,7 +49298,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C402" s="35" t="str">
-        <x:v>longitudinalFrame</x:v>
+        <x:v>longitudinalFrameLoadDistributionFactorF4</x:v>
       </x:c>
       <x:c r="D402" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49314,7 +49316,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C403" s="35" t="str">
-        <x:v>longitudinalFrameLoadDistributionFactorF4</x:v>
+        <x:v>longitudinalFrameShearFactorF5</x:v>
       </x:c>
       <x:c r="D403" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49332,7 +49334,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C404" s="35" t="str">
-        <x:v>longitudinalFrameShearFactorF5</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D404" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49350,7 +49352,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C405" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>significantlyDifferentBoundaryConditions</x:v>
       </x:c>
       <x:c r="D405" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49368,7 +49370,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C406" s="35" t="str">
-        <x:v>significantlyDifferentBoundaryConditions</x:v>
+        <x:v>spacing</x:v>
       </x:c>
       <x:c r="D406" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49386,7 +49388,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C407" s="35" t="str">
-        <x:v>spacing</x:v>
+        <x:v>span</x:v>
       </x:c>
       <x:c r="D407" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49404,7 +49406,7 @@
         <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="C408" s="35" t="str">
-        <x:v>span</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D408" s="35" t="str">
         <x:v>longitudinalFrame</x:v>
@@ -49416,18 +49418,20 @@
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="38" t="str">
-        <x:v>TRF-048</x:v>
+        <x:v>TRF-049</x:v>
       </x:c>
       <x:c r="B409" s="35" t="str">
-        <x:v>longitudinalFrame</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="C409" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>bracketEdgeStiffened</x:v>
       </x:c>
       <x:c r="D409" s="35" t="str">
-        <x:v>longitudinalFrame</x:v>
-      </x:c>
-      <x:c r="E409" s="35" t="str"/>
+        <x:v>connectionBracket</x:v>
+      </x:c>
+      <x:c r="E409" s="35" t="str">
+        <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
+      </x:c>
       <x:c r="F409" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -49440,7 +49444,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C410" s="35" t="str">
-        <x:v>bracketEdgeStiffened</x:v>
+        <x:v>bracketThickness</x:v>
       </x:c>
       <x:c r="D410" s="35" t="str">
         <x:v>connectionBracket</x:v>
@@ -49460,7 +49464,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C411" s="35" t="str">
-        <x:v>bracketThickness</x:v>
+        <x:v>bucklingStiffening</x:v>
       </x:c>
       <x:c r="D411" s="35" t="str">
         <x:v>connectionBracket</x:v>
@@ -49480,10 +49484,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C412" s="35" t="str">
-        <x:v>bucklingStiffening</x:v>
+        <x:v>connectionBracket</x:v>
       </x:c>
       <x:c r="D412" s="35" t="str">
-        <x:v>connectionBracket</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E412" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49500,10 +49504,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C413" s="35" t="str">
-        <x:v>connectionBracket</x:v>
+        <x:v>effectiveAttachmentConfirmed</x:v>
       </x:c>
       <x:c r="D413" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="E413" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49520,10 +49524,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C414" s="35" t="str">
-        <x:v>effectiveAttachmentConfirmed</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="D414" s="35" t="str">
-        <x:v>frameAttachment</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E414" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49540,7 +49544,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C415" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="D415" s="35" t="str">
         <x:v>frame</x:v>
@@ -49560,7 +49564,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C416" s="35" t="str">
-        <x:v>frameAttachment</x:v>
+        <x:v>frameWebThickness</x:v>
       </x:c>
       <x:c r="D416" s="35" t="str">
         <x:v>frame</x:v>
@@ -49580,10 +49584,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C417" s="35" t="str">
-        <x:v>frameWebThickness</x:v>
+        <x:v>hasAttachedSupportingStructure</x:v>
       </x:c>
       <x:c r="D417" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="E417" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49600,7 +49604,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C418" s="35" t="str">
-        <x:v>hasAttachedSupportingStructure</x:v>
+        <x:v>hasConnectionBracket</x:v>
       </x:c>
       <x:c r="D418" s="35" t="str">
         <x:v>frameAttachment</x:v>
@@ -49620,10 +49624,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C419" s="35" t="str">
-        <x:v>hasConnectionBracket</x:v>
+        <x:v>hasFrameAttachment</x:v>
       </x:c>
       <x:c r="D419" s="35" t="str">
-        <x:v>frameAttachment</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E419" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49640,7 +49644,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C420" s="35" t="str">
-        <x:v>hasFrameAttachment</x:v>
+        <x:v>hasSupportingBulkhead</x:v>
       </x:c>
       <x:c r="D420" s="35" t="str">
         <x:v>frame</x:v>
@@ -49660,10 +49664,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C421" s="35" t="str">
-        <x:v>hasSupportingBulkhead</x:v>
+        <x:v>hasSupportingStructureAttachment</x:v>
       </x:c>
       <x:c r="D421" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>supportingStructure</x:v>
       </x:c>
       <x:c r="E421" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49680,10 +49684,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C422" s="35" t="str">
-        <x:v>hasSupportingStructureAttachment</x:v>
+        <x:v>hasSupportingWebFrame</x:v>
       </x:c>
       <x:c r="D422" s="35" t="str">
-        <x:v>supportingStructure</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E422" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49700,7 +49704,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C423" s="35" t="str">
-        <x:v>hasSupportingWebFrame</x:v>
+        <x:v>longitudinalFrame</x:v>
       </x:c>
       <x:c r="D423" s="35" t="str">
         <x:v>frame</x:v>
@@ -49720,7 +49724,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C424" s="35" t="str">
-        <x:v>longitudinalFrame</x:v>
+        <x:v>passesThroughSupportingStructure</x:v>
       </x:c>
       <x:c r="D424" s="35" t="str">
         <x:v>frame</x:v>
@@ -49740,10 +49744,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C425" s="35" t="str">
-        <x:v>passesThroughSupportingStructure</x:v>
+        <x:v>similarAttachmentConstructionPresent</x:v>
       </x:c>
       <x:c r="D425" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="E425" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49760,10 +49764,10 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C426" s="35" t="str">
-        <x:v>similarAttachmentConstructionPresent</x:v>
+        <x:v>supportingStructure</x:v>
       </x:c>
       <x:c r="D426" s="35" t="str">
-        <x:v>frameAttachment</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E426" s="35" t="str">
         <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
@@ -49780,7 +49784,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C427" s="35" t="str">
-        <x:v>supportingStructure</x:v>
+        <x:v>terminatesAtDeckOrIceStringer</x:v>
       </x:c>
       <x:c r="D427" s="35" t="str">
         <x:v>frame</x:v>
@@ -49800,7 +49804,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C428" s="35" t="str">
-        <x:v>terminatesAtDeckOrIceStringer</x:v>
+        <x:v>transverseFrame</x:v>
       </x:c>
       <x:c r="D428" s="35" t="str">
         <x:v>frame</x:v>
@@ -49820,7 +49824,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C429" s="35" t="str">
-        <x:v>transverseFrame</x:v>
+        <x:v>webPlateConnectionSideCount</x:v>
       </x:c>
       <x:c r="D429" s="35" t="str">
         <x:v>frame</x:v>
@@ -49840,7 +49844,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C430" s="35" t="str">
-        <x:v>webPlateConnectionSideCount</x:v>
+        <x:v>withinIceStrengthenedArea</x:v>
       </x:c>
       <x:c r="D430" s="35" t="str">
         <x:v>frame</x:v>
@@ -49854,20 +49858,18 @@
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="38" t="str">
-        <x:v>TRF-049</x:v>
+        <x:v>TRF-050</x:v>
       </x:c>
       <x:c r="B431" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="C431" s="35" t="str">
-        <x:v>withinIceStrengthenedArea</x:v>
+        <x:v>doubleContinuousWeld</x:v>
       </x:c>
       <x:c r="D431" s="35" t="str">
-        <x:v>frame</x:v>
-      </x:c>
-      <x:c r="E431" s="35" t="str">
-        <x:v>Target frame subclasses directly and keep attachment evidence on frameAttachment: effectiveAttachmentConfirmed, similarAttachmentConstructionPresent, hasAttachedSupportingStructure, and hasConnectionBracket. | Use SHACL Core for local presence, datatype, cardinality, and unit checks; reserve bounded SPARQL for shared attachment identity and bracketThickness &gt;= frameWebThickness.</x:v>
-      </x:c>
+        <x:v>frameAttachment</x:v>
+      </x:c>
+      <x:c r="E431" s="35" t="str"/>
       <x:c r="F431" s="35" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
@@ -49880,7 +49882,7 @@
         <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="C432" s="35" t="str">
-        <x:v>doubleContinuousWeld</x:v>
+        <x:v>frameShellAttachment</x:v>
       </x:c>
       <x:c r="D432" s="35" t="str">
         <x:v>frameAttachment</x:v>
@@ -49898,7 +49900,7 @@
         <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="C433" s="35" t="str">
-        <x:v>frameShellAttachment</x:v>
+        <x:v>frameShellWeldType</x:v>
       </x:c>
       <x:c r="D433" s="35" t="str">
         <x:v>frameAttachment</x:v>
@@ -49916,7 +49918,7 @@
         <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="C434" s="35" t="str">
-        <x:v>frameShellWeldType</x:v>
+        <x:v>scallopingPresent</x:v>
       </x:c>
       <x:c r="D434" s="35" t="str">
         <x:v>frameAttachment</x:v>
@@ -49934,7 +49936,7 @@
         <x:v>frameAttachment</x:v>
       </x:c>
       <x:c r="C435" s="35" t="str">
-        <x:v>scallopingPresent</x:v>
+        <x:v>shellPlateButtCrossing</x:v>
       </x:c>
       <x:c r="D435" s="35" t="str">
         <x:v>frameAttachment</x:v>
@@ -49946,16 +49948,16 @@
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="38" t="str">
-        <x:v>TRF-050</x:v>
+        <x:v>TRF-051</x:v>
       </x:c>
       <x:c r="B436" s="35" t="str">
-        <x:v>frameAttachment</x:v>
+        <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C436" s="35" t="str">
-        <x:v>shellPlateButtCrossing</x:v>
+        <x:v>adjacentFrameHeight</x:v>
       </x:c>
       <x:c r="D436" s="35" t="str">
-        <x:v>frameAttachment</x:v>
+        <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="E436" s="35" t="str"/>
       <x:c r="F436" s="35" t="str">
@@ -49970,7 +49972,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C437" s="35" t="str">
-        <x:v>adjacentFrameHeight</x:v>
+        <x:v>bulkhead</x:v>
       </x:c>
       <x:c r="D437" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -49988,7 +49990,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C438" s="35" t="str">
-        <x:v>bulkhead</x:v>
+        <x:v>corrosionAbrasionAddition</x:v>
       </x:c>
       <x:c r="D438" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50006,7 +50008,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C439" s="35" t="str">
-        <x:v>corrosionAbrasionAddition</x:v>
+        <x:v>deckStructure</x:v>
       </x:c>
       <x:c r="D439" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50024,7 +50026,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C440" s="35" t="str">
-        <x:v>deckStructure</x:v>
+        <x:v>flatBarSection</x:v>
       </x:c>
       <x:c r="D440" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50042,7 +50044,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C441" s="35" t="str">
-        <x:v>flatBarSection</x:v>
+        <x:v>frameProfileType</x:v>
       </x:c>
       <x:c r="D441" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50060,7 +50062,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C442" s="35" t="str">
-        <x:v>frameProfileType</x:v>
+        <x:v>frameWebThickness</x:v>
       </x:c>
       <x:c r="D442" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50078,7 +50080,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C443" s="35" t="str">
-        <x:v>frameWebThickness</x:v>
+        <x:v>hullStructuralSteelGrade</x:v>
       </x:c>
       <x:c r="D443" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50096,7 +50098,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C444" s="35" t="str">
-        <x:v>hullStructuralSteelGrade</x:v>
+        <x:v>inLieuOfFrame</x:v>
       </x:c>
       <x:c r="D444" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50114,7 +50116,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C445" s="35" t="str">
-        <x:v>inLieuOfFrame</x:v>
+        <x:v>netShellPlatingThickness</x:v>
       </x:c>
       <x:c r="D445" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50132,7 +50134,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C446" s="35" t="str">
-        <x:v>netShellPlatingThickness</x:v>
+        <x:v>profileSection</x:v>
       </x:c>
       <x:c r="D446" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50150,7 +50152,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C447" s="35" t="str">
-        <x:v>profileSection</x:v>
+        <x:v>tankBottom</x:v>
       </x:c>
       <x:c r="D447" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50168,7 +50170,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C448" s="35" t="str">
-        <x:v>tankBottom</x:v>
+        <x:v>tankBoundaryPlating</x:v>
       </x:c>
       <x:c r="D448" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50186,7 +50188,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C449" s="35" t="str">
-        <x:v>tankBoundaryPlating</x:v>
+        <x:v>tankTop</x:v>
       </x:c>
       <x:c r="D449" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50204,7 +50206,7 @@
         <x:v>hullStructure</x:v>
       </x:c>
       <x:c r="C450" s="35" t="str">
-        <x:v>tankTop</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D450" s="35" t="str">
         <x:v>hullStructure</x:v>
@@ -50216,16 +50218,16 @@
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="38" t="str">
-        <x:v>TRF-051</x:v>
+        <x:v>TRF-052</x:v>
       </x:c>
       <x:c r="B451" s="35" t="str">
-        <x:v>hullStructure</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="C451" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>antitrippingSupportSpacing</x:v>
       </x:c>
       <x:c r="D451" s="35" t="str">
-        <x:v>hullStructure</x:v>
+        <x:v>frame</x:v>
       </x:c>
       <x:c r="E451" s="35" t="str"/>
       <x:c r="F451" s="35" t="str">
@@ -50240,7 +50242,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C452" s="35" t="str">
-        <x:v>antitrippingSupportSpacing</x:v>
+        <x:v>bowRegion</x:v>
       </x:c>
       <x:c r="D452" s="35" t="str">
         <x:v>frame</x:v>
@@ -50258,7 +50260,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C453" s="35" t="str">
-        <x:v>bowRegion</x:v>
+        <x:v>equivalentSupportStatusByDirectCalculation</x:v>
       </x:c>
       <x:c r="D453" s="35" t="str">
         <x:v>frame</x:v>
@@ -50276,7 +50278,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C454" s="35" t="str">
-        <x:v>equivalentSupportStatusByDirectCalculation</x:v>
+        <x:v>frameAsymmetrical</x:v>
       </x:c>
       <x:c r="D454" s="35" t="str">
         <x:v>frame</x:v>
@@ -50294,7 +50296,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C455" s="35" t="str">
-        <x:v>frameAsymmetrical</x:v>
+        <x:v>frameSpan</x:v>
       </x:c>
       <x:c r="D455" s="35" t="str">
         <x:v>frame</x:v>
@@ -50312,7 +50314,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C456" s="35" t="str">
-        <x:v>frameSpan</x:v>
+        <x:v>frameWebAngleToShell</x:v>
       </x:c>
       <x:c r="D456" s="35" t="str">
         <x:v>frame</x:v>
@@ -50330,7 +50332,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C457" s="35" t="str">
-        <x:v>frameWebAngleToShell</x:v>
+        <x:v>hasAntitrippingSupportRegion</x:v>
       </x:c>
       <x:c r="D457" s="35" t="str">
         <x:v>frame</x:v>
@@ -50348,7 +50350,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C458" s="35" t="str">
-        <x:v>hasAntitrippingSupportRegion</x:v>
+        <x:v>iceClass</x:v>
       </x:c>
       <x:c r="D458" s="35" t="str">
         <x:v>frame</x:v>
@@ -50366,7 +50368,7 @@
         <x:v>frame</x:v>
       </x:c>
       <x:c r="C459" s="35" t="str">
-        <x:v>iceClass</x:v>
+        <x:v>midbodyRegion</x:v>
       </x:c>
       <x:c r="D459" s="35" t="str">
         <x:v>frame</x:v>
@@ -50378,16 +50380,16 @@
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="38" t="str">
-        <x:v>TRF-052</x:v>
+        <x:v>TRF-053</x:v>
       </x:c>
       <x:c r="B460" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C460" s="35" t="str">
-        <x:v>midbodyRegion</x:v>
+        <x:v>designIceLoadHeight</x:v>
       </x:c>
       <x:c r="D460" s="35" t="str">
-        <x:v>frame</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="E460" s="35" t="str"/>
       <x:c r="F460" s="35" t="str">
@@ -50402,7 +50404,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C461" s="35" t="str">
-        <x:v>designIceLoadHeight</x:v>
+        <x:v>designLineLoad</x:v>
       </x:c>
       <x:c r="D461" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50420,7 +50422,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C462" s="35" t="str">
-        <x:v>designLineLoad</x:v>
+        <x:v>frameMomentFactorM</x:v>
       </x:c>
       <x:c r="D462" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50438,7 +50440,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C463" s="35" t="str">
-        <x:v>frameMomentFactorM</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D463" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50456,7 +50458,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C464" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="D464" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50474,7 +50476,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C465" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>iceStringerDistributionFactorF6</x:v>
       </x:c>
       <x:c r="D465" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50492,7 +50494,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C466" s="35" t="str">
-        <x:v>iceStringerDistributionFactorF6</x:v>
+        <x:v>iceStringerSafetyFactorF7</x:v>
       </x:c>
       <x:c r="D466" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50510,7 +50512,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C467" s="35" t="str">
-        <x:v>iceStringerSafetyFactorF7</x:v>
+        <x:v>iceStringerShearFactorF8</x:v>
       </x:c>
       <x:c r="D467" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50528,7 +50530,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C468" s="35" t="str">
-        <x:v>iceStringerShearFactorF8</x:v>
+        <x:v>locatedWithinIceBelt</x:v>
       </x:c>
       <x:c r="D468" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50546,7 +50548,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C469" s="35" t="str">
-        <x:v>locatedWithinIceBelt</x:v>
+        <x:v>requiredShearArea</x:v>
       </x:c>
       <x:c r="D469" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50564,7 +50566,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C470" s="35" t="str">
-        <x:v>requiredShearArea</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D470" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50582,7 +50584,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C471" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>span</x:v>
       </x:c>
       <x:c r="D471" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50600,7 +50602,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C472" s="35" t="str">
-        <x:v>span</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D472" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50612,13 +50614,13 @@
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="38" t="str">
-        <x:v>TRF-053</x:v>
+        <x:v>TRF-054</x:v>
       </x:c>
       <x:c r="B473" s="35" t="str">
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C473" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>designIceLoadHeight</x:v>
       </x:c>
       <x:c r="D473" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50636,7 +50638,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C474" s="35" t="str">
-        <x:v>designIceLoadHeight</x:v>
+        <x:v>designLineLoad</x:v>
       </x:c>
       <x:c r="D474" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50654,7 +50656,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C475" s="35" t="str">
-        <x:v>designLineLoad</x:v>
+        <x:v>distanceToAdjacentIceStringer</x:v>
       </x:c>
       <x:c r="D475" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50672,7 +50674,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C476" s="35" t="str">
-        <x:v>distanceToAdjacentIceStringer</x:v>
+        <x:v>distanceToIceBelt</x:v>
       </x:c>
       <x:c r="D476" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50690,7 +50692,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C477" s="35" t="str">
-        <x:v>distanceToIceBelt</x:v>
+        <x:v>frameMomentFactorM</x:v>
       </x:c>
       <x:c r="D477" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50708,7 +50710,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C478" s="35" t="str">
-        <x:v>frameMomentFactorM</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D478" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50726,7 +50728,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C479" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="D479" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50744,7 +50746,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C480" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>locatedOutsideIceBelt</x:v>
       </x:c>
       <x:c r="D480" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50762,7 +50764,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C481" s="35" t="str">
-        <x:v>locatedOutsideIceBelt</x:v>
+        <x:v>outsideIceBeltDistributionFactorF9</x:v>
       </x:c>
       <x:c r="D481" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50780,7 +50782,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C482" s="35" t="str">
-        <x:v>outsideIceBeltDistributionFactorF9</x:v>
+        <x:v>outsideIceBeltFactor</x:v>
       </x:c>
       <x:c r="D482" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50798,7 +50800,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C483" s="35" t="str">
-        <x:v>outsideIceBeltFactor</x:v>
+        <x:v>outsideIceBeltSafetyFactorF10</x:v>
       </x:c>
       <x:c r="D483" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50816,7 +50818,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C484" s="35" t="str">
-        <x:v>outsideIceBeltSafetyFactorF10</x:v>
+        <x:v>outsideIceBeltShearFactorF11</x:v>
       </x:c>
       <x:c r="D484" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50834,7 +50836,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C485" s="35" t="str">
-        <x:v>outsideIceBeltShearFactorF11</x:v>
+        <x:v>requiredShearArea</x:v>
       </x:c>
       <x:c r="D485" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50852,7 +50854,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C486" s="35" t="str">
-        <x:v>requiredShearArea</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D486" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50870,7 +50872,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C487" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>span</x:v>
       </x:c>
       <x:c r="D487" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50888,7 +50890,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C488" s="35" t="str">
-        <x:v>span</x:v>
+        <x:v>stringerSpan</x:v>
       </x:c>
       <x:c r="D488" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50906,7 +50908,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C489" s="35" t="str">
-        <x:v>stringerSpan</x:v>
+        <x:v>supportsIceStrengthenedFrames</x:v>
       </x:c>
       <x:c r="D489" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50924,7 +50926,7 @@
         <x:v>iceStringer</x:v>
       </x:c>
       <x:c r="C490" s="35" t="str">
-        <x:v>supportsIceStrengthenedFrames</x:v>
+        <x:v>yieldStrength</x:v>
       </x:c>
       <x:c r="D490" s="35" t="str">
         <x:v>iceStringer</x:v>
@@ -50936,16 +50938,16 @@
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="38" t="str">
-        <x:v>TRF-054</x:v>
+        <x:v>TRF-055</x:v>
       </x:c>
       <x:c r="B491" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C491" s="35" t="str">
-        <x:v>yieldStrength</x:v>
+        <x:v>abreastOfHatch</x:v>
       </x:c>
       <x:c r="D491" s="35" t="str">
-        <x:v>iceStringer</x:v>
+        <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="E491" s="35" t="str"/>
       <x:c r="F491" s="35" t="str">
@@ -50960,7 +50962,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C492" s="35" t="str">
-        <x:v>abreastOfHatch</x:v>
+        <x:v>actualSectionModulus</x:v>
       </x:c>
       <x:c r="D492" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -50978,7 +50980,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C493" s="35" t="str">
-        <x:v>actualSectionModulus</x:v>
+        <x:v>actualShearArea</x:v>
       </x:c>
       <x:c r="D493" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -50996,7 +50998,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C494" s="35" t="str">
-        <x:v>actualShearArea</x:v>
+        <x:v>designLineLoad</x:v>
       </x:c>
       <x:c r="D494" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51014,7 +51016,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C495" s="35" t="str">
-        <x:v>designLineLoad</x:v>
+        <x:v>hatchOpeningLength</x:v>
       </x:c>
       <x:c r="D495" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51032,7 +51034,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C496" s="35" t="str">
-        <x:v>hatchOpeningLength</x:v>
+        <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="D496" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51050,7 +51052,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C497" s="35" t="str">
-        <x:v>narrowDeckStrip</x:v>
+        <x:v>permittedReducedLineLoad</x:v>
       </x:c>
       <x:c r="D497" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51068,7 +51070,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C498" s="35" t="str">
-        <x:v>permittedReducedLineLoad</x:v>
+        <x:v>reducedLineLoadApprovedByClassificationSociety</x:v>
       </x:c>
       <x:c r="D498" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51086,7 +51088,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C499" s="35" t="str">
-        <x:v>reducedLineLoadApprovedByClassificationSociety</x:v>
+        <x:v>requiredSectionModulus</x:v>
       </x:c>
       <x:c r="D499" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51104,7 +51106,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C500" s="35" t="str">
-        <x:v>requiredSectionModulus</x:v>
+        <x:v>requiredShearArea</x:v>
       </x:c>
       <x:c r="D500" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51122,7 +51124,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C501" s="35" t="str">
-        <x:v>requiredShearArea</x:v>
+        <x:v>scantlingApprovalStatus</x:v>
       </x:c>
       <x:c r="D501" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51140,7 +51142,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C502" s="35" t="str">
-        <x:v>scantlingApprovalStatus</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D502" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51158,7 +51160,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C503" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>servesAsIceStringer</x:v>
       </x:c>
       <x:c r="D503" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51176,7 +51178,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C504" s="35" t="str">
-        <x:v>servesAsIceStringer</x:v>
+        <x:v>shipBreadth</x:v>
       </x:c>
       <x:c r="D504" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51194,7 +51196,7 @@
         <x:v>narrowDeckStrip</x:v>
       </x:c>
       <x:c r="C505" s="35" t="str">
-        <x:v>shipBreadth</x:v>
+        <x:v>veryLongHatchOpening</x:v>
       </x:c>
       <x:c r="D505" s="35" t="str">
         <x:v>narrowDeckStrip</x:v>
@@ -51206,16 +51208,16 @@
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="38" t="str">
-        <x:v>TRF-055</x:v>
+        <x:v>TRF-056</x:v>
       </x:c>
       <x:c r="B506" s="35" t="str">
-        <x:v>narrowDeckStrip</x:v>
+        <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C506" s="35" t="str">
-        <x:v>veryLongHatchOpening</x:v>
+        <x:v>hasHatchCoverDesignEvidence</x:v>
       </x:c>
       <x:c r="D506" s="35" t="str">
-        <x:v>narrowDeckStrip</x:v>
+        <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="E506" s="35" t="str"/>
       <x:c r="F506" s="35" t="str">
@@ -51230,7 +51232,7 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C507" s="35" t="str">
-        <x:v>hasHatchCoverDesignEvidence</x:v>
+        <x:v>hasHatchFittingDesignEvidence</x:v>
       </x:c>
       <x:c r="D507" s="35" t="str">
         <x:v>weatherdeckHatch</x:v>
@@ -51248,10 +51250,10 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C508" s="35" t="str">
-        <x:v>hasHatchFittingDesignEvidence</x:v>
+        <x:v>hasWeatherdeckHatch</x:v>
       </x:c>
       <x:c r="D508" s="35" t="str">
-        <x:v>weatherdeckHatch</x:v>
+        <x:v>ship</x:v>
       </x:c>
       <x:c r="E508" s="35" t="str"/>
       <x:c r="F508" s="35" t="str">
@@ -51266,10 +51268,10 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C509" s="35" t="str">
-        <x:v>hasWeatherdeckHatch</x:v>
+        <x:v>hatchCoverDesignEvidence</x:v>
       </x:c>
       <x:c r="D509" s="35" t="str">
-        <x:v>ship</x:v>
+        <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="E509" s="35" t="str"/>
       <x:c r="F509" s="35" t="str">
@@ -51284,7 +51286,7 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C510" s="35" t="str">
-        <x:v>hatchCoverDesignEvidence</x:v>
+        <x:v>hatchFittingDesignEvidence</x:v>
       </x:c>
       <x:c r="D510" s="35" t="str">
         <x:v>weatherdeckHatch</x:v>
@@ -51302,7 +51304,7 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C511" s="35" t="str">
-        <x:v>hatchFittingDesignEvidence</x:v>
+        <x:v>hatchOpeningLength</x:v>
       </x:c>
       <x:c r="D511" s="35" t="str">
         <x:v>weatherdeckHatch</x:v>
@@ -51320,7 +51322,7 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C512" s="35" t="str">
-        <x:v>hatchOpeningLength</x:v>
+        <x:v>shipBreadth</x:v>
       </x:c>
       <x:c r="D512" s="35" t="str">
         <x:v>weatherdeckHatch</x:v>
@@ -51338,7 +51340,7 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C513" s="35" t="str">
-        <x:v>shipBreadth</x:v>
+        <x:v>shipSideDeflection</x:v>
       </x:c>
       <x:c r="D513" s="35" t="str">
         <x:v>weatherdeckHatch</x:v>
@@ -51356,7 +51358,7 @@
         <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="C514" s="35" t="str">
-        <x:v>shipSideDeflection</x:v>
+        <x:v>weatherdeckHatch</x:v>
       </x:c>
       <x:c r="D514" s="35" t="str">
         <x:v>weatherdeckHatch</x:v>
@@ -51368,16 +51370,16 @@
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="38" t="str">
-        <x:v>TRF-056</x:v>
+        <x:v>TRF-057</x:v>
       </x:c>
       <x:c r="B515" s="35" t="str">
-        <x:v>weatherdeckHatch</x:v>
+        <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C515" s="35" t="str">
-        <x:v>weatherdeckHatch</x:v>
+        <x:v>iceLoadHeight</x:v>
       </x:c>
       <x:c r="D515" s="35" t="str">
-        <x:v>weatherdeckHatch</x:v>
+        <x:v>webFrame</x:v>
       </x:c>
       <x:c r="E515" s="35" t="str"/>
       <x:c r="F515" s="35" t="str">
@@ -51392,7 +51394,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C516" s="35" t="str">
-        <x:v>iceLoadHeight</x:v>
+        <x:v>iceLoadSourceType</x:v>
       </x:c>
       <x:c r="D516" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51410,7 +51412,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C517" s="35" t="str">
-        <x:v>iceLoadSourceType</x:v>
+        <x:v>icePressure</x:v>
       </x:c>
       <x:c r="D517" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51428,7 +51430,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C518" s="35" t="str">
-        <x:v>icePressure</x:v>
+        <x:v>iceStringerLoadSource</x:v>
       </x:c>
       <x:c r="D518" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51446,7 +51448,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C519" s="35" t="str">
-        <x:v>iceStringerLoadSource</x:v>
+        <x:v>loadLengthParameter</x:v>
       </x:c>
       <x:c r="D519" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51464,7 +51466,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C520" s="35" t="str">
-        <x:v>loadLengthParameter</x:v>
+        <x:v>longitudinalFramingLoadSource</x:v>
       </x:c>
       <x:c r="D520" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51482,7 +51484,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C521" s="35" t="str">
-        <x:v>longitudinalFramingLoadSource</x:v>
+        <x:v>minimumLineLoad</x:v>
       </x:c>
       <x:c r="D521" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51500,7 +51502,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C522" s="35" t="str">
-        <x:v>minimumLineLoad</x:v>
+        <x:v>webFrameIceLoad</x:v>
       </x:c>
       <x:c r="D522" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51518,7 +51520,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C523" s="35" t="str">
-        <x:v>webFrameIceLoad</x:v>
+        <x:v>webFrameSafetyFactor</x:v>
       </x:c>
       <x:c r="D523" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51536,7 +51538,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C524" s="35" t="str">
-        <x:v>webFrameSafetyFactor</x:v>
+        <x:v>webFrameSpacing</x:v>
       </x:c>
       <x:c r="D524" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51548,13 +51550,13 @@
     </x:row>
     <x:row r="525">
       <x:c r="A525" s="38" t="str">
-        <x:v>TRF-057</x:v>
+        <x:v>TRF-058</x:v>
       </x:c>
       <x:c r="B525" s="35" t="str">
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C525" s="35" t="str">
-        <x:v>webFrameSpacing</x:v>
+        <x:v>adjustedIceLoadForce</x:v>
       </x:c>
       <x:c r="D525" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51572,7 +51574,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C526" s="35" t="str">
-        <x:v>adjustedIceLoadForce</x:v>
+        <x:v>iceLoadForce</x:v>
       </x:c>
       <x:c r="D526" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51590,7 +51592,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C527" s="35" t="str">
-        <x:v>iceLoadForce</x:v>
+        <x:v>stringerOutsideIceBeltHeight</x:v>
       </x:c>
       <x:c r="D527" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51608,7 +51610,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C528" s="35" t="str">
-        <x:v>stringerOutsideIceBeltHeight</x:v>
+        <x:v>stringerSpan</x:v>
       </x:c>
       <x:c r="D528" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51626,7 +51628,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C529" s="35" t="str">
-        <x:v>stringerSpan</x:v>
+        <x:v>supportedStringerOutsideIceBelt</x:v>
       </x:c>
       <x:c r="D529" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51638,13 +51640,13 @@
     </x:row>
     <x:row r="530">
       <x:c r="A530" s="38" t="str">
-        <x:v>TRF-058</x:v>
+        <x:v>TRF-059</x:v>
       </x:c>
       <x:c r="B530" s="35" t="str">
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C530" s="35" t="str">
-        <x:v>supportedStringerOutsideIceBelt</x:v>
+        <x:v>freeFlangeArea</x:v>
       </x:c>
       <x:c r="D530" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51662,7 +51664,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C531" s="35" t="str">
-        <x:v>freeFlangeArea</x:v>
+        <x:v>freeFlangeToWebAreaRatio</x:v>
       </x:c>
       <x:c r="D531" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51680,7 +51682,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C532" s="35" t="str">
-        <x:v>freeFlangeToWebAreaRatio</x:v>
+        <x:v>maximumCalculatedShearForce</x:v>
       </x:c>
       <x:c r="D532" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51698,7 +51700,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C533" s="35" t="str">
-        <x:v>maximumCalculatedShearForce</x:v>
+        <x:v>requiredShearArea</x:v>
       </x:c>
       <x:c r="D533" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51716,7 +51718,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C534" s="35" t="str">
-        <x:v>requiredShearArea</x:v>
+        <x:v>sectionModulus</x:v>
       </x:c>
       <x:c r="D534" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51734,7 +51736,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C535" s="35" t="str">
-        <x:v>sectionModulus</x:v>
+        <x:v>webFrameShearDistributionFactorF13</x:v>
       </x:c>
       <x:c r="D535" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51752,7 +51754,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C536" s="35" t="str">
-        <x:v>webFrameShearDistributionFactorF13</x:v>
+        <x:v>webFrameShearFactorAlpha</x:v>
       </x:c>
       <x:c r="D536" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51770,7 +51772,7 @@
         <x:v>webFrame</x:v>
       </x:c>
       <x:c r="C537" s="35" t="str">
-        <x:v>webFrameShearFactorAlpha</x:v>
+        <x:v>webPlateArea</x:v>
       </x:c>
       <x:c r="D537" s="35" t="str">
         <x:v>webFrame</x:v>
@@ -51781,43 +51783,25 @@
       </x:c>
     </x:row>
     <x:row r="538">
-      <x:c r="A538" s="38" t="str">
+      <x:c r="A538" s="57" t="str">
         <x:v>TRF-059</x:v>
       </x:c>
-      <x:c r="B538" s="35" t="str">
+      <x:c r="B538" s="36" t="str">
         <x:v>webFrame</x:v>
       </x:c>
-      <x:c r="C538" s="35" t="str">
-        <x:v>webPlateArea</x:v>
-      </x:c>
-      <x:c r="D538" s="35" t="str">
+      <x:c r="C538" s="36" t="str">
+        <x:v>yieldStrength</x:v>
+      </x:c>
+      <x:c r="D538" s="36" t="str">
         <x:v>webFrame</x:v>
       </x:c>
-      <x:c r="E538" s="35" t="str"/>
-      <x:c r="F538" s="35" t="str">
+      <x:c r="E538" s="36" t="str"/>
+      <x:c r="F538" s="36" t="str">
         <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
       </x:c>
     </x:row>
-    <x:row r="539">
-      <x:c r="A539" s="57" t="str">
-        <x:v>TRF-059</x:v>
-      </x:c>
-      <x:c r="B539" s="36" t="str">
-        <x:v>webFrame</x:v>
-      </x:c>
-      <x:c r="C539" s="36" t="str">
-        <x:v>yieldStrength</x:v>
-      </x:c>
-      <x:c r="D539" s="36" t="str">
-        <x:v>webFrame</x:v>
-      </x:c>
-      <x:c r="E539" s="36" t="str"/>
-      <x:c r="F539" s="36" t="str">
-        <x:v>AUTHORITATIVE_REQUIREMENT_SCOPED</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F5:F539">
+  <x:conditionalFormatting sqref="F5:F538">
     <x:cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="READY"/>
     <x:cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="COMPLETE"/>
     <x:cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="NEW"/>
@@ -51826,7 +51810,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa99a82d6d04c17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11010a1a684d451a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51987,24 +51971,75 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="57" t="str">
+      <x:c r="A11" s="38" t="str">
         <x:v>ALL</x:v>
       </x:c>
-      <x:c r="B11" s="36" t="str">
+      <x:c r="B11" s="35" t="str">
         <x:v>STATUS_CLASSIFICATION</x:v>
       </x:c>
-      <x:c r="C11" s="57" t="str">
+      <x:c r="C11" s="38" t="str">
         <x:v>Matcher exhaustion was previously labeled VOCABULARY_GAP even when a canonical term might exist outside retrieval candidates.</x:v>
       </x:c>
-      <x:c r="D11" s="57" t="str">
+      <x:c r="D11" s="38" t="str">
         <x:v>RESOLVED</x:v>
       </x:c>
-      <x:c r="E11" s="57" t="str">
+      <x:c r="E11" s="38" t="str">
         <x:v>Runtime status is TERM_RESOLUTION_UNRESOLVED; a true vocabulary gap requires registry/index audit evidence.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="38" t="str">
+        <x:v>TRF-025</x:v>
+      </x:c>
+      <x:c r="B12" s="35" t="str">
+        <x:v>UNIT_METADATA_GAP</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="str">
+        <x:v>C1 and C2 are formula outputs whose units were left unspecified, causing the generated shape and canonical fixtures to disagree.</x:v>
+      </x:c>
+      <x:c r="D12" s="38" t="str">
+        <x:v>RESOLVED_R8_1</x:v>
+      </x:c>
+      <x:c r="E12" s="38" t="str">
+        <x:v>Assign unit:N to C1 and C2 from the verified dimensions of every additive formula term.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="38" t="str">
+        <x:v>TRF-030</x:v>
+      </x:c>
+      <x:c r="B13" s="35" t="str">
+        <x:v>OVER_STRONG_EXCLUSIVITY</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="str">
+        <x:v>The semantic validator correctly noted that the clause does not prohibit a case from recording both coordinates.</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="str">
+        <x:v>RESOLVED_R8_1</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="str">
+        <x:v>Remove the R8 exclusivePropertyGroups declaration; retain the requirement for several vertical and horizontal cases.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="57" t="str">
+        <x:v>TRF-022</x:v>
+      </x:c>
+      <x:c r="B14" s="36" t="str">
+        <x:v>UNSUPPORTED_APPLICABILITY</x:v>
+      </x:c>
+      <x:c r="C14" s="57" t="str">
+        <x:v>The R8 shape inherited a construction-date branch although clause 3.2.2 contains no date condition, allowing the deliberate failure to pass.</x:v>
+      </x:c>
+      <x:c r="D14" s="57" t="str">
+        <x:v>RESOLVED_R8_1</x:v>
+      </x:c>
+      <x:c r="E14" s="57" t="str">
+        <x:v>Remove constructionStageDate from the TRF-022 scoped requirement index.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D5:D11">
+  <x:conditionalFormatting sqref="D5:D14">
     <x:cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="READY"/>
     <x:cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="COMPLETE"/>
     <x:cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="NEW"/>
@@ -52013,7 +52048,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21939078b1104166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R432eb26481d9402c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52159,7 +52194,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K5" s="34" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L5" s="34" t="str">
         <x:v>YES</x:v>
@@ -52200,7 +52235,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K6" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L6" s="35" t="str">
         <x:v>YES</x:v>
@@ -52241,7 +52276,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K7" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L7" s="35" t="str">
         <x:v>YES</x:v>
@@ -52282,7 +52317,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K8" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L8" s="35" t="str">
         <x:v>YES</x:v>
@@ -52323,7 +52358,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K9" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L9" s="35" t="str">
         <x:v>YES</x:v>
@@ -52364,7 +52399,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K10" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L10" s="35" t="str">
         <x:v>YES</x:v>
@@ -52405,7 +52440,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K11" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L11" s="35" t="str">
         <x:v>YES</x:v>
@@ -52446,7 +52481,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K12" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L12" s="35" t="str">
         <x:v>YES</x:v>
@@ -52487,7 +52522,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K13" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L13" s="35" t="str">
         <x:v>YES</x:v>
@@ -52528,7 +52563,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K14" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L14" s="35" t="str">
         <x:v>YES</x:v>
@@ -52569,7 +52604,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K15" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L15" s="35" t="str">
         <x:v>YES</x:v>
@@ -52610,7 +52645,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K16" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L16" s="35" t="str">
         <x:v>YES</x:v>
@@ -52651,7 +52686,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K17" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L17" s="35" t="str">
         <x:v>YES</x:v>
@@ -52692,7 +52727,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K18" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L18" s="35" t="str">
         <x:v>YES</x:v>
@@ -52733,7 +52768,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K19" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L19" s="35" t="str">
         <x:v>YES</x:v>
@@ -52774,7 +52809,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K20" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L20" s="35" t="str">
         <x:v>YES</x:v>
@@ -52815,7 +52850,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K21" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L21" s="35" t="str">
         <x:v>YES</x:v>
@@ -52856,7 +52891,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K22" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L22" s="35" t="str">
         <x:v>YES</x:v>
@@ -52897,7 +52932,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K23" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L23" s="35" t="str">
         <x:v>YES</x:v>
@@ -52938,7 +52973,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K24" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L24" s="35" t="str">
         <x:v>YES</x:v>
@@ -52979,7 +53014,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K25" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L25" s="35" t="str">
         <x:v>YES</x:v>
@@ -53020,7 +53055,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K26" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L26" s="35" t="str">
         <x:v>YES</x:v>
@@ -53061,7 +53096,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K27" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L27" s="35" t="str">
         <x:v>YES</x:v>
@@ -53102,7 +53137,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K28" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L28" s="35" t="str">
         <x:v>YES</x:v>
@@ -53143,7 +53178,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K29" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L29" s="35" t="str">
         <x:v>YES</x:v>
@@ -53184,7 +53219,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K30" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L30" s="35" t="str">
         <x:v>YES</x:v>
@@ -53225,7 +53260,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K31" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L31" s="35" t="str">
         <x:v>YES</x:v>
@@ -53266,7 +53301,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K32" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L32" s="35" t="str">
         <x:v>YES</x:v>
@@ -53307,7 +53342,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K33" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L33" s="35" t="str">
         <x:v>YES</x:v>
@@ -53348,7 +53383,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K34" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L34" s="35" t="str">
         <x:v>YES</x:v>
@@ -53389,7 +53424,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K35" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L35" s="35" t="str">
         <x:v>YES</x:v>
@@ -53430,7 +53465,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K36" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L36" s="35" t="str">
         <x:v>YES</x:v>
@@ -53471,7 +53506,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K37" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L37" s="35" t="str">
         <x:v>YES</x:v>
@@ -53512,7 +53547,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="K38" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L38" s="35" t="str">
         <x:v>YES</x:v>
@@ -53553,7 +53588,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="K39" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L39" s="35" t="str">
         <x:v>YES</x:v>
@@ -53594,7 +53629,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="K40" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L40" s="35" t="str">
         <x:v>YES</x:v>
@@ -53635,7 +53670,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="K41" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L41" s="35" t="str">
         <x:v>YES</x:v>
@@ -53676,7 +53711,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="K42" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L42" s="35" t="str">
         <x:v>YES</x:v>
@@ -53717,7 +53752,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="K43" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L43" s="35" t="str">
         <x:v>YES</x:v>
@@ -53758,7 +53793,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="K44" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L44" s="35" t="str">
         <x:v>YES</x:v>
@@ -53799,7 +53834,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="K45" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L45" s="35" t="str">
         <x:v>YES</x:v>
@@ -53840,7 +53875,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="K46" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L46" s="35" t="str">
         <x:v>YES</x:v>
@@ -53881,7 +53916,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="K47" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L47" s="35" t="str">
         <x:v>YES</x:v>
@@ -53922,7 +53957,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="K48" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L48" s="35" t="str">
         <x:v>YES</x:v>
@@ -53963,7 +53998,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="K49" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L49" s="35" t="str">
         <x:v>YES</x:v>
@@ -54004,7 +54039,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K50" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L50" s="35" t="str">
         <x:v>YES</x:v>
@@ -54045,7 +54080,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K51" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L51" s="35" t="str">
         <x:v>YES</x:v>
@@ -54086,7 +54121,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K52" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L52" s="35" t="str">
         <x:v>YES</x:v>
@@ -54127,7 +54162,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K53" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L53" s="35" t="str">
         <x:v>YES</x:v>
@@ -54168,7 +54203,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K54" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L54" s="35" t="str">
         <x:v>YES</x:v>
@@ -54209,7 +54244,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="K55" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L55" s="35" t="str">
         <x:v>YES</x:v>
@@ -54250,7 +54285,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="K56" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L56" s="35" t="str">
         <x:v>YES</x:v>
@@ -54291,7 +54326,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="K57" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L57" s="35" t="str">
         <x:v>YES</x:v>
@@ -54332,7 +54367,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="K58" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L58" s="35" t="str">
         <x:v>YES</x:v>
@@ -54367,13 +54402,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-022/trf-022_01_pass.ttl</x:v>
       </x:c>
       <x:c r="I59" s="35" t="str">
-        <x:v>fd1979d8add8fa73070e1b390baaa8ea3292a4f8817481db06eccbb43e7c59bc</x:v>
+        <x:v>e1257cf715e1651bccefa5f5fa00b68cb31d831d91793d35c1b5dcf33fa8629b</x:v>
       </x:c>
       <x:c r="J59" s="54" t="n">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K59" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L59" s="35" t="str">
         <x:v>YES</x:v>
@@ -54408,13 +54443,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-022/trf-022_02_fail.ttl</x:v>
       </x:c>
       <x:c r="I60" s="35" t="str">
-        <x:v>d617b6e6de457ff6b0506160cbf9391f2134901b75d89fab651178614ad7422e</x:v>
+        <x:v>dff0198facecd1ffa189224e0c8c4d015e5bb1d1c76baf0a7e5c2bbd6e01685b</x:v>
       </x:c>
       <x:c r="J60" s="54" t="n">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K60" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L60" s="35" t="str">
         <x:v>YES</x:v>
@@ -54449,13 +54484,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-022/trf-022_03_boundary.ttl</x:v>
       </x:c>
       <x:c r="I61" s="35" t="str">
-        <x:v>187d2b1c7fd85648eec6fd627d49d8adf7b71e6f94c3877463a049bfee4c182c</x:v>
+        <x:v>548895049e70674e814ef4100d660a0d95772fa2df7ea558f2a34f38e8f8b8b2</x:v>
       </x:c>
       <x:c r="J61" s="54" t="n">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K61" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L61" s="35" t="str">
         <x:v>YES</x:v>
@@ -54496,7 +54531,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K62" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L62" s="35" t="str">
         <x:v>YES</x:v>
@@ -54537,7 +54572,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K63" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L63" s="35" t="str">
         <x:v>YES</x:v>
@@ -54578,7 +54613,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K64" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L64" s="35" t="str">
         <x:v>YES</x:v>
@@ -54619,7 +54654,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K65" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L65" s="35" t="str">
         <x:v>YES</x:v>
@@ -54660,7 +54695,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K66" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L66" s="35" t="str">
         <x:v>YES</x:v>
@@ -54701,7 +54736,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K67" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L67" s="35" t="str">
         <x:v>YES</x:v>
@@ -54736,13 +54771,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-025/trf-025_01_pass.ttl</x:v>
       </x:c>
       <x:c r="I68" s="35" t="str">
-        <x:v>9a3660b799573e778a698b6c6845fb1fdbff36fe68e5ce6622eddbac6d57f527</x:v>
+        <x:v>7047f27bc417a1580ddbb99fb0801e01656d65d4d2f2a5da06b51a2684008d14</x:v>
       </x:c>
       <x:c r="J68" s="54" t="n">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K68" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L68" s="35" t="str">
         <x:v>YES</x:v>
@@ -54777,13 +54812,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-025/trf-025_02_fail.ttl</x:v>
       </x:c>
       <x:c r="I69" s="35" t="str">
-        <x:v>8fb23a341dede880ab84622cfde9be7c603f0dad442784ec23c85a81a979969b</x:v>
+        <x:v>6fb706d9e669f17674cc33581ee105129404e597200061c796a9a799463d9259</x:v>
       </x:c>
       <x:c r="J69" s="54" t="n">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K69" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L69" s="35" t="str">
         <x:v>YES</x:v>
@@ -54818,13 +54853,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-025/trf-025_03_boundary.ttl</x:v>
       </x:c>
       <x:c r="I70" s="35" t="str">
-        <x:v>bc7ac85048b2cd5ffa746a357da278fe0020f735be18c9552a9b771c6e324ee5</x:v>
+        <x:v>a8d7d2eb86ee3fe6dfae00cb0cbf3d5366f23c19591007b15772b3ebb22c9c9a</x:v>
       </x:c>
       <x:c r="J70" s="54" t="n">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K70" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L70" s="35" t="str">
         <x:v>YES</x:v>
@@ -54859,13 +54894,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-026/trf-026_01_pass.ttl</x:v>
       </x:c>
       <x:c r="I71" s="35" t="str">
-        <x:v>458de456baab5f69c0a56b4c75f73d18b41c38c1e1632ac816195dd9a9776f63</x:v>
+        <x:v>87bf0fb9306f75c4d9f83a7f7b95a6c5b6797b1e21cbdbd4bdfbc9e9e1fd7483</x:v>
       </x:c>
       <x:c r="J71" s="54" t="n">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K71" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L71" s="35" t="str">
         <x:v>YES</x:v>
@@ -54900,13 +54935,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-026/trf-026_02_fail.ttl</x:v>
       </x:c>
       <x:c r="I72" s="35" t="str">
-        <x:v>841a02bf7c613cb2994345554a660272a7c85cfdec232809015930198e2af594</x:v>
+        <x:v>66b4ee8dfd887744239e534c225cd58783390e0c9418c16142a02e9bf225c86a</x:v>
       </x:c>
       <x:c r="J72" s="54" t="n">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K72" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L72" s="35" t="str">
         <x:v>YES</x:v>
@@ -54941,13 +54976,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-026/trf-026_03_boundary.ttl</x:v>
       </x:c>
       <x:c r="I73" s="35" t="str">
-        <x:v>464e177b804a7bf85739ff641582b66ed11e40a30f5964080866d6648cb0b5ee</x:v>
+        <x:v>67e6c3079e3c312e9a2cfe1981389abcd20796a89e180eb9603a91ae5c3b48e4</x:v>
       </x:c>
       <x:c r="J73" s="54" t="n">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K73" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L73" s="35" t="str">
         <x:v>YES</x:v>
@@ -54988,7 +55023,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="K74" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L74" s="35" t="str">
         <x:v>YES</x:v>
@@ -55029,7 +55064,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="K75" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L75" s="35" t="str">
         <x:v>YES</x:v>
@@ -55070,7 +55105,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="K76" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L76" s="35" t="str">
         <x:v>YES</x:v>
@@ -55111,7 +55146,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="K77" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L77" s="35" t="str">
         <x:v>YES</x:v>
@@ -55152,7 +55187,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="K78" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L78" s="35" t="str">
         <x:v>YES</x:v>
@@ -55193,7 +55228,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="K79" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L79" s="35" t="str">
         <x:v>YES</x:v>
@@ -55234,7 +55269,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K80" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L80" s="35" t="str">
         <x:v>YES</x:v>
@@ -55275,7 +55310,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K81" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L81" s="35" t="str">
         <x:v>YES</x:v>
@@ -55316,7 +55351,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K82" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L82" s="35" t="str">
         <x:v>YES</x:v>
@@ -55357,7 +55392,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K83" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L83" s="35" t="str">
         <x:v>YES</x:v>
@@ -55398,7 +55433,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K84" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L84" s="35" t="str">
         <x:v>YES</x:v>
@@ -55439,7 +55474,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K85" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L85" s="35" t="str">
         <x:v>YES</x:v>
@@ -55480,7 +55515,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="K86" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L86" s="35" t="str">
         <x:v>YES</x:v>
@@ -55521,7 +55556,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="K87" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L87" s="35" t="str">
         <x:v>YES</x:v>
@@ -55562,7 +55597,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="K88" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L88" s="35" t="str">
         <x:v>YES</x:v>
@@ -55603,7 +55638,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K89" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L89" s="35" t="str">
         <x:v>YES</x:v>
@@ -55644,7 +55679,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K90" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L90" s="35" t="str">
         <x:v>YES</x:v>
@@ -55685,7 +55720,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K91" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L91" s="35" t="str">
         <x:v>YES</x:v>
@@ -55726,7 +55761,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K92" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L92" s="35" t="str">
         <x:v>YES</x:v>
@@ -55767,7 +55802,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K93" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L93" s="35" t="str">
         <x:v>YES</x:v>
@@ -55808,7 +55843,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="K94" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L94" s="35" t="str">
         <x:v>YES</x:v>
@@ -55843,13 +55878,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-037/trf-037_01_pass.ttl</x:v>
       </x:c>
       <x:c r="I95" s="35" t="str">
-        <x:v>2885b66eb02b260ba10d7a64543be2d6b95b434b7a3a333447f3f9bc5c71d9bd</x:v>
+        <x:v>99a84b0d560fade36f2c4fc848bd3974c0522e334d81719a6af980b28603cf5d</x:v>
       </x:c>
       <x:c r="J95" s="54" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K95" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L95" s="35" t="str">
         <x:v>YES</x:v>
@@ -55884,13 +55919,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-037/trf-037_02_fail.ttl</x:v>
       </x:c>
       <x:c r="I96" s="35" t="str">
-        <x:v>2ce56859b64d59ffb16ac2b4217924df6c798aa6a986e7da34e32301f6398e7b</x:v>
+        <x:v>c1c8675d75ed95134a626e7e53cc5dca474266f09d3bd9ae10304657d42ffca5</x:v>
       </x:c>
       <x:c r="J96" s="54" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K96" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L96" s="35" t="str">
         <x:v>YES</x:v>
@@ -55925,13 +55960,13 @@
         <x:v>INPUTS/DEVELOPMENT_CALIBRATION/BATCH_01_FIRST_50/rdf_fixtures/TRF-037/trf-037_03_boundary.ttl</x:v>
       </x:c>
       <x:c r="I97" s="35" t="str">
-        <x:v>ce75c111ec17d41f1de1fb20b997cb6b39d4c480dc5ba34240274d230ef56a80</x:v>
+        <x:v>bbd451b59e6b445443ec9fd8b7fd022f81577cb1d03976fa01c99e0bb4dd7bb3</x:v>
       </x:c>
       <x:c r="J97" s="54" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K97" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L97" s="35" t="str">
         <x:v>YES</x:v>
@@ -55972,7 +56007,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K98" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L98" s="35" t="str">
         <x:v>YES</x:v>
@@ -56013,7 +56048,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K99" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L99" s="35" t="str">
         <x:v>YES</x:v>
@@ -56054,7 +56089,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K100" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L100" s="35" t="str">
         <x:v>YES</x:v>
@@ -56095,7 +56130,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="K101" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L101" s="35" t="str">
         <x:v>YES</x:v>
@@ -56136,7 +56171,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="K102" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L102" s="35" t="str">
         <x:v>YES</x:v>
@@ -56177,7 +56212,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="K103" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L103" s="35" t="str">
         <x:v>YES</x:v>
@@ -56218,7 +56253,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K104" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L104" s="35" t="str">
         <x:v>YES</x:v>
@@ -56259,7 +56294,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K105" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L105" s="35" t="str">
         <x:v>YES</x:v>
@@ -56300,7 +56335,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K106" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L106" s="35" t="str">
         <x:v>YES</x:v>
@@ -56341,7 +56376,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="K107" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L107" s="35" t="str">
         <x:v>YES</x:v>
@@ -56382,7 +56417,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="K108" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L108" s="35" t="str">
         <x:v>YES</x:v>
@@ -56423,7 +56458,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="K109" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L109" s="35" t="str">
         <x:v>YES</x:v>
@@ -56464,7 +56499,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K110" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L110" s="35" t="str">
         <x:v>YES</x:v>
@@ -56505,7 +56540,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K111" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L111" s="35" t="str">
         <x:v>YES</x:v>
@@ -56546,7 +56581,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="K112" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L112" s="35" t="str">
         <x:v>YES</x:v>
@@ -56587,7 +56622,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="K113" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L113" s="35" t="str">
         <x:v>YES</x:v>
@@ -56628,7 +56663,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="K114" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L114" s="35" t="str">
         <x:v>YES</x:v>
@@ -56669,7 +56704,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="K115" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L115" s="35" t="str">
         <x:v>YES</x:v>
@@ -56710,7 +56745,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="K116" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L116" s="35" t="str">
         <x:v>YES</x:v>
@@ -56751,7 +56786,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K117" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L117" s="35" t="str">
         <x:v>YES</x:v>
@@ -56792,7 +56827,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="K118" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L118" s="35" t="str">
         <x:v>YES</x:v>
@@ -56833,7 +56868,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="K119" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L119" s="35" t="str">
         <x:v>YES</x:v>
@@ -56874,7 +56909,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="K120" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L120" s="35" t="str">
         <x:v>YES</x:v>
@@ -56915,7 +56950,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="K121" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L121" s="35" t="str">
         <x:v>YES</x:v>
@@ -56956,7 +56991,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K122" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L122" s="35" t="str">
         <x:v>YES</x:v>
@@ -56997,7 +57032,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K123" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L123" s="35" t="str">
         <x:v>YES</x:v>
@@ -57038,7 +57073,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K124" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L124" s="35" t="str">
         <x:v>YES</x:v>
@@ -57079,7 +57114,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K125" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L125" s="35" t="str">
         <x:v>YES</x:v>
@@ -57120,7 +57155,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K126" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L126" s="35" t="str">
         <x:v>YES</x:v>
@@ -57161,7 +57196,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K127" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L127" s="35" t="str">
         <x:v>YES</x:v>
@@ -57202,7 +57237,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K128" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L128" s="35" t="str">
         <x:v>YES</x:v>
@@ -57243,7 +57278,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K129" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L129" s="35" t="str">
         <x:v>YES</x:v>
@@ -57284,7 +57319,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K130" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L130" s="35" t="str">
         <x:v>YES</x:v>
@@ -57325,7 +57360,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K131" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L131" s="35" t="str">
         <x:v>YES</x:v>
@@ -57366,7 +57401,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K132" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L132" s="35" t="str">
         <x:v>YES</x:v>
@@ -57407,7 +57442,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K133" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L133" s="35" t="str">
         <x:v>YES</x:v>
@@ -57448,7 +57483,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="K134" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L134" s="35" t="str">
         <x:v>YES</x:v>
@@ -57489,7 +57524,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="K135" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L135" s="35" t="str">
         <x:v>YES</x:v>
@@ -57530,7 +57565,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="K136" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L136" s="35" t="str">
         <x:v>YES</x:v>
@@ -57571,7 +57606,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="K137" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L137" s="35" t="str">
         <x:v>YES</x:v>
@@ -57612,7 +57647,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="K138" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L138" s="35" t="str">
         <x:v>YES</x:v>
@@ -57653,7 +57688,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="K139" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L139" s="35" t="str">
         <x:v>YES</x:v>
@@ -57694,7 +57729,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K140" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L140" s="35" t="str">
         <x:v>YES</x:v>
@@ -57735,7 +57770,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K141" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L141" s="35" t="str">
         <x:v>YES</x:v>
@@ -57776,7 +57811,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K142" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L142" s="35" t="str">
         <x:v>YES</x:v>
@@ -57817,7 +57852,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="K143" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L143" s="35" t="str">
         <x:v>YES</x:v>
@@ -57858,7 +57893,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="K144" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L144" s="35" t="str">
         <x:v>YES</x:v>
@@ -57899,7 +57934,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="K145" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L145" s="35" t="str">
         <x:v>YES</x:v>
@@ -57940,7 +57975,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="K146" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L146" s="35" t="str">
         <x:v>YES</x:v>
@@ -57981,7 +58016,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="K147" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L147" s="35" t="str">
         <x:v>YES</x:v>
@@ -58022,7 +58057,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="K148" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L148" s="35" t="str">
         <x:v>YES</x:v>
@@ -58063,7 +58098,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K149" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L149" s="35" t="str">
         <x:v>YES</x:v>
@@ -58104,7 +58139,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K150" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L150" s="35" t="str">
         <x:v>YES</x:v>
@@ -58145,7 +58180,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="K151" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L151" s="35" t="str">
         <x:v>YES</x:v>
@@ -58186,7 +58221,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="K152" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L152" s="35" t="str">
         <x:v>YES</x:v>
@@ -58227,7 +58262,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="K153" s="35" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L153" s="35" t="str">
         <x:v>YES</x:v>
@@ -58268,7 +58303,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="K154" s="36" t="str">
-        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R7</x:v>
+        <x:v>VOCAB-DEV-2026-08-13-BATCH01-R8.1-POSTCONFIRMATION</x:v>
       </x:c>
       <x:c r="L154" s="36" t="str">
         <x:v>YES</x:v>
@@ -58287,7 +58322,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e3eb27496cb4451"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9cb5afc5b3f4c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>